--- a/VerveStacks_BIH_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BIH_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BIH_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E51ADDD-E474-4ADD-8492-495E4994BAD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAA75198-0960-4338-9959-CC620C17D801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2995" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3145" uniqueCount="527">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -485,25 +485,43 @@
     <t>g_Bijeljina_BIH-Bratunac_BIH</t>
   </si>
   <si>
-    <t>g_Doboj_BIH-Bijeljina_BIH</t>
+    <t>g_Doboj_BIH-Tuzla_BIH</t>
+  </si>
+  <si>
+    <t>g_Mostar_BIH-Sarajevo_BIH</t>
   </si>
   <si>
     <t>g_Mostar_BIH-Trebinje_BIH</t>
   </si>
   <si>
-    <t>g_Mostar_BIH-Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>g_Mostar_BIH-Zenica_BIH</t>
-  </si>
-  <si>
-    <t>g_Prijedor_BIH-Zenica_BIH</t>
+    <t>g_Orasje_BIH-Bijeljina_BIH</t>
+  </si>
+  <si>
+    <t>g_Orasje_BIH-Doboj_BIH</t>
+  </si>
+  <si>
+    <t>g_Prijedor_BIH-Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>g_Sarajevo_BIH-Bratunac_BIH</t>
+  </si>
+  <si>
+    <t>g_Sarajevo_BIH-Tuzla_BIH</t>
   </si>
   <si>
     <t>g_SirokiBrijeg_BIH-Mostar_BIH</t>
   </si>
   <si>
-    <t>g_SirokiBrijeg_BIH-Zenica_BIH</t>
+    <t>g_SirokiBrijeg_BIH-Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>g_SirokiBrijeg_BIH-Travnik_BIH</t>
+  </si>
+  <si>
+    <t>g_Travnik_BIH-Mostar_BIH</t>
+  </si>
+  <si>
+    <t>g_Travnik_BIH-Prijedor_BIH</t>
   </si>
   <si>
     <t>g_Trebinje_BIH-Bratunac_BIH</t>
@@ -515,22 +533,13 @@
     <t>g_Tuzla_BIH-Bijeljina_BIH</t>
   </si>
   <si>
-    <t>g_Tuzla_BIH-Doboj_BIH</t>
+    <t>g_Tuzla_BIH-Orasje_BIH</t>
   </si>
   <si>
     <t>g_Tuzla_BIH-Prijedor_BIH</t>
   </si>
   <si>
-    <t>g_Tuzla_BIH-Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>g_Vogosca_BIH-Bratunac_BIH</t>
-  </si>
-  <si>
-    <t>g_Zenica_BIH-Prijedor_BIH</t>
-  </si>
-  <si>
-    <t>g_Zenica_BIH-Tuzla_BIH</t>
+    <t>g_Tuzla_BIH-Sarajevo_BIH</t>
   </si>
   <si>
     <t>~tfm_ins-at</t>
@@ -557,15 +566,15 @@
     <t>e_demand_Mostar_BIH</t>
   </si>
   <si>
-    <t>e_demand_Vogosca_BIH</t>
-  </si>
-  <si>
     <t>e_demand_Bijeljina_BIH</t>
   </si>
   <si>
     <t>e_demand_Trebinje_BIH</t>
   </si>
   <si>
+    <t>e_demand_Travnik_BIH</t>
+  </si>
+  <si>
     <t>e_demand_Doboj_BIH</t>
   </si>
   <si>
@@ -575,27 +584,30 @@
     <t>e_demand_Bratunac_BIH</t>
   </si>
   <si>
-    <t>e_demand_Zenica_BIH</t>
-  </si>
-  <si>
     <t>e_demand_SirokiBrijeg_BIH</t>
   </si>
   <si>
+    <t>e_demand_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>e_demand_Sarajevo_BIH</t>
+  </si>
+  <si>
     <t>ev_battery_Prijedor_BIH</t>
   </si>
   <si>
     <t>ev_battery_Mostar_BIH</t>
   </si>
   <si>
-    <t>ev_battery_Vogosca_BIH</t>
-  </si>
-  <si>
     <t>ev_battery_Bijeljina_BIH</t>
   </si>
   <si>
     <t>ev_battery_Trebinje_BIH</t>
   </si>
   <si>
+    <t>ev_battery_Travnik_BIH</t>
+  </si>
+  <si>
     <t>ev_battery_Doboj_BIH</t>
   </si>
   <si>
@@ -605,27 +617,30 @@
     <t>ev_battery_Bratunac_BIH</t>
   </si>
   <si>
-    <t>ev_battery_Zenica_BIH</t>
-  </si>
-  <si>
     <t>ev_battery_SirokiBrijeg_BIH</t>
   </si>
   <si>
+    <t>ev_battery_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>ev_battery_Sarajevo_BIH</t>
+  </si>
+  <si>
     <t>H2prd_Elc_PEM_Prijedor_BIH</t>
   </si>
   <si>
     <t>H2prd_Elc_PEM_Mostar_BIH</t>
   </si>
   <si>
-    <t>H2prd_Elc_PEM_Vogosca_BIH</t>
-  </si>
-  <si>
     <t>H2prd_Elc_PEM_Bijeljina_BIH</t>
   </si>
   <si>
     <t>H2prd_Elc_PEM_Trebinje_BIH</t>
   </si>
   <si>
+    <t>H2prd_Elc_PEM_Travnik_BIH</t>
+  </si>
+  <si>
     <t>H2prd_Elc_PEM_Doboj_BIH</t>
   </si>
   <si>
@@ -635,27 +650,30 @@
     <t>H2prd_Elc_PEM_Bratunac_BIH</t>
   </si>
   <si>
-    <t>H2prd_Elc_PEM_Zenica_BIH</t>
-  </si>
-  <si>
     <t>H2prd_Elc_PEM_SirokiBrijeg_BIH</t>
   </si>
   <si>
+    <t>H2prd_Elc_PEM_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Sarajevo_BIH</t>
+  </si>
+  <si>
     <t>H2prd_Elc_ALK_Prijedor_BIH</t>
   </si>
   <si>
     <t>H2prd_Elc_ALK_Mostar_BIH</t>
   </si>
   <si>
-    <t>H2prd_Elc_ALK_Vogosca_BIH</t>
-  </si>
-  <si>
     <t>H2prd_Elc_ALK_Bijeljina_BIH</t>
   </si>
   <si>
     <t>H2prd_Elc_ALK_Trebinje_BIH</t>
   </si>
   <si>
+    <t>H2prd_Elc_ALK_Travnik_BIH</t>
+  </si>
+  <si>
     <t>H2prd_Elc_ALK_Doboj_BIH</t>
   </si>
   <si>
@@ -665,16 +683,19 @@
     <t>H2prd_Elc_ALK_Bratunac_BIH</t>
   </si>
   <si>
-    <t>H2prd_Elc_ALK_Zenica_BIH</t>
-  </si>
-  <si>
     <t>H2prd_Elc_ALK_SirokiBrijeg_BIH</t>
   </si>
   <si>
+    <t>H2prd_Elc_ALK_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Sarajevo_BIH</t>
+  </si>
+  <si>
     <t>elc_industry</t>
   </si>
   <si>
-    <t>h_demand_Zenica_BIH</t>
+    <t>h_demand_Sarajevo_BIH</t>
   </si>
   <si>
     <t>het_buildings</t>
@@ -701,15 +722,15 @@
     <t>e_Mostar_BIH</t>
   </si>
   <si>
-    <t>e_Vogosca_BIH</t>
-  </si>
-  <si>
     <t>e_Bijeljina_BIH</t>
   </si>
   <si>
     <t>e_Trebinje_BIH</t>
   </si>
   <si>
+    <t>e_Travnik_BIH</t>
+  </si>
+  <si>
     <t>e_Doboj_BIH</t>
   </si>
   <si>
@@ -719,13 +740,16 @@
     <t>e_Bratunac_BIH</t>
   </si>
   <si>
-    <t>e_Zenica_BIH</t>
-  </si>
-  <si>
     <t>e_SirokiBrijeg_BIH</t>
   </si>
   <si>
-    <t>h_Zenica_BIH</t>
+    <t>e_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>e_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>h_Sarajevo_BIH</t>
   </si>
   <si>
     <t>h_Tuzla_BIH</t>
@@ -845,60 +869,6 @@
     <t>en_hp_air_10mw_Mostar_BIH</t>
   </si>
   <si>
-    <t>en_gas_ccgt_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>en_nuclear_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>en_biomass_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>h_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_Vogosca_BIH</t>
-  </si>
-  <si>
     <t>en_gas_ccgt_Bijeljina_BIH</t>
   </si>
   <si>
@@ -1007,6 +977,60 @@
     <t>en_hp_air_10mw_Trebinje_BIH</t>
   </si>
   <si>
+    <t>en_gas_ccgt_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>en_nuclear_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>en_biomass_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>h_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Travnik_BIH</t>
+  </si>
+  <si>
     <t>en_gas_ccgt_Doboj_BIH</t>
   </si>
   <si>
@@ -1166,57 +1190,6 @@
     <t>en_hp_air_10mw_Bratunac_BIH</t>
   </si>
   <si>
-    <t>en_gas_ccgt_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>en_nuclear_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>en_biomass_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_Zenica_BIH</t>
-  </si>
-  <si>
     <t>en_gas_ccgt_SirokiBrijeg_BIH</t>
   </si>
   <si>
@@ -1271,6 +1244,111 @@
     <t>en_hp_air_10mw_SirokiBrijeg_BIH</t>
   </si>
   <si>
+    <t>en_gas_ccgt_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>en_nuclear_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>en_biomass_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>h_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>en_nuclear_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>en_biomass_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Sarajevo_BIH</t>
+  </si>
+  <si>
     <t>EN_STG8hbNREL_Prijedor_BIH</t>
   </si>
   <si>
@@ -1283,12 +1361,6 @@
     <t>EN_STG4hbNREL_Mostar_BIH</t>
   </si>
   <si>
-    <t>EN_STG8hbNREL_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Vogosca_BIH</t>
-  </si>
-  <si>
     <t>EN_STG8hbNREL_Bijeljina_BIH</t>
   </si>
   <si>
@@ -1301,6 +1373,12 @@
     <t>EN_STG4hbNREL_Trebinje_BIH</t>
   </si>
   <si>
+    <t>EN_STG8hbNREL_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Travnik_BIH</t>
+  </si>
+  <si>
     <t>EN_STG8hbNREL_Doboj_BIH</t>
   </si>
   <si>
@@ -1319,18 +1397,24 @@
     <t>EN_STG4hbNREL_Bratunac_BIH</t>
   </si>
   <si>
-    <t>EN_STG8hbNREL_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_Zenica_BIH</t>
-  </si>
-  <si>
     <t>EN_STG8hbNREL_SirokiBrijeg_BIH</t>
   </si>
   <si>
     <t>EN_STG4hbNREL_SirokiBrijeg_BIH</t>
   </si>
   <si>
+    <t>EN_STG8hbNREL_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Sarajevo_BIH</t>
+  </si>
+  <si>
     <t>ELC</t>
   </si>
   <si>
@@ -1379,15 +1463,15 @@
     <t>p_co2_Mostar_BIH-ogci11364</t>
   </si>
   <si>
-    <t>p_co2_Vogosca_BIH-ogci11364</t>
-  </si>
-  <si>
     <t>p_co2_Bijeljina_BIH-ogci11364</t>
   </si>
   <si>
     <t>p_co2_Trebinje_BIH-ogci11364</t>
   </si>
   <si>
+    <t>p_co2_Travnik_BIH-ogci11364</t>
+  </si>
+  <si>
     <t>p_co2_Doboj_BIH-ogci11364</t>
   </si>
   <si>
@@ -1397,12 +1481,15 @@
     <t>p_co2_Bratunac_BIH-ogci11364</t>
   </si>
   <si>
-    <t>p_co2_Zenica_BIH-ogci11364</t>
-  </si>
-  <si>
     <t>p_co2_SirokiBrijeg_BIH-ogci11364</t>
   </si>
   <si>
+    <t>p_co2_Orasje_BIH-ogci11364</t>
+  </si>
+  <si>
+    <t>p_co2_Sarajevo_BIH-ogci11364</t>
+  </si>
+  <si>
     <t>flo_emis</t>
   </si>
   <si>
@@ -1412,15 +1499,15 @@
     <t>co2_Mostar_BIH</t>
   </si>
   <si>
-    <t>co2_Vogosca_BIH</t>
-  </si>
-  <si>
     <t>co2_Bijeljina_BIH</t>
   </si>
   <si>
     <t>co2_Trebinje_BIH</t>
   </si>
   <si>
+    <t>co2_Travnik_BIH</t>
+  </si>
+  <si>
     <t>co2_Doboj_BIH</t>
   </si>
   <si>
@@ -1430,37 +1517,40 @@
     <t>co2_Bratunac_BIH</t>
   </si>
   <si>
-    <t>co2_Zenica_BIH</t>
-  </si>
-  <si>
     <t>co2_SirokiBrijeg_BIH</t>
   </si>
   <si>
+    <t>co2_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>co2_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105453-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110403-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110404-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000110433_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_m_coal_subcritical_G100000110402-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110405-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105454-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000109595_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000105455-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110404-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_supercritical_G100000110433_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105453-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_m_coal_subcritical_G100000110402-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000105454-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110405-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000109595_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_coal_subcritical_G100000110403-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_coal_supercritical_G100000102880_ccs-rf</t>
@@ -2114,8 +2204,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{857553AE-6C49-4855-9E3C-D97491527005}">
-  <dimension ref="B2:AG243"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{503C28D0-3447-487F-84AD-7AFB3731D8C4}">
+  <dimension ref="B2:AG267"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="2" spans="2:33" x14ac:dyDescent="0.45">
@@ -2123,13 +2213,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P2" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="U2" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.45">
@@ -2149,13 +2239,13 @@
         <v>3</v>
       </c>
       <c r="I3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="L3" t="s">
         <v>13</v>
@@ -2164,25 +2254,25 @@
         <v>3</v>
       </c>
       <c r="Q3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="R3" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="U3" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="V3" t="s">
         <v>3</v>
       </c>
       <c r="W3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="X3" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="AA3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.45">
@@ -2199,61 +2289,61 @@
         <v>0.99441999999999997</v>
       </c>
       <c r="H4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J4">
+        <v>0.1376937968579082</v>
+      </c>
+      <c r="K4" t="s">
+        <v>142</v>
+      </c>
+      <c r="L4" t="s">
+        <v>141</v>
+      </c>
+      <c r="P4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>193</v>
+      </c>
+      <c r="R4" t="s">
+        <v>194</v>
+      </c>
+      <c r="U4" t="s">
+        <v>112</v>
+      </c>
+      <c r="V4" t="s">
+        <v>208</v>
+      </c>
+      <c r="W4" t="s">
+        <v>193</v>
+      </c>
+      <c r="X4" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA4" t="s">
         <v>137</v>
       </c>
-      <c r="I4" t="s">
-        <v>138</v>
-      </c>
-      <c r="J4">
-        <v>0.15716430349956209</v>
-      </c>
-      <c r="K4" t="s">
-        <v>139</v>
-      </c>
-      <c r="L4" t="s">
-        <v>138</v>
-      </c>
-      <c r="P4" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>186</v>
-      </c>
-      <c r="R4" t="s">
-        <v>187</v>
-      </c>
-      <c r="U4" t="s">
-        <v>112</v>
-      </c>
-      <c r="V4" t="s">
-        <v>200</v>
-      </c>
-      <c r="W4" t="s">
-        <v>186</v>
-      </c>
-      <c r="X4" t="s">
-        <v>201</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>134</v>
-      </c>
       <c r="AB4" t="s">
-        <v>400</v>
+        <v>428</v>
       </c>
       <c r="AC4" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="AD4" t="s">
-        <v>403</v>
+        <v>431</v>
       </c>
       <c r="AE4" t="s">
-        <v>404</v>
+        <v>432</v>
       </c>
       <c r="AF4" t="s">
-        <v>405</v>
+        <v>433</v>
       </c>
       <c r="AG4" t="s">
-        <v>408</v>
+        <v>436</v>
       </c>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.45">
@@ -2261,55 +2351,55 @@
         <v>117</v>
       </c>
       <c r="C5">
-        <v>1.7874764334110815</v>
+        <v>0.49155601918804742</v>
       </c>
       <c r="D5">
-        <v>107.80000000000001</v>
+        <v>52.800000000000004</v>
       </c>
       <c r="E5">
-        <v>0.99412</v>
+        <v>0.99712000000000001</v>
       </c>
       <c r="H5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J5">
-        <v>8.5256535804089525E-2</v>
+        <v>9.7710613758789755E-2</v>
       </c>
       <c r="K5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="Q5" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="R5" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U5" t="s">
         <v>112</v>
       </c>
       <c r="V5" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="W5" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="X5" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="AA5" t="s">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="AB5" t="s">
-        <v>401</v>
+        <v>429</v>
       </c>
       <c r="AC5">
         <v>2</v>
@@ -2318,10 +2408,10 @@
         <v>0</v>
       </c>
       <c r="AF5" t="s">
-        <v>406</v>
+        <v>434</v>
       </c>
       <c r="AG5" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.45">
@@ -2329,55 +2419,55 @@
         <v>118</v>
       </c>
       <c r="C6">
-        <v>1.7874764334110815</v>
+        <v>2.2790324525991292</v>
       </c>
       <c r="D6">
-        <v>75.900000000000006</v>
+        <v>104.50000000000001</v>
       </c>
       <c r="E6">
-        <v>0.99585999999999997</v>
+        <v>0.99429999999999996</v>
       </c>
       <c r="H6" t="s">
+        <v>144</v>
+      </c>
+      <c r="I6" t="s">
         <v>141</v>
       </c>
-      <c r="I6" t="s">
-        <v>138</v>
-      </c>
       <c r="J6">
-        <v>0.20086231039523153</v>
+        <v>8.1627754367396457E-2</v>
       </c>
       <c r="K6" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L6" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="Q6" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="R6" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U6" t="s">
         <v>112</v>
       </c>
       <c r="V6" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="W6" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="X6" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="AA6" t="s">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="AB6" t="s">
-        <v>401</v>
+        <v>429</v>
       </c>
       <c r="AD6">
         <v>2</v>
@@ -2386,7 +2476,7 @@
         <v>0</v>
       </c>
       <c r="AF6" t="s">
-        <v>407</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.45">
@@ -2397,46 +2487,46 @@
         <v>1.7874764334110815</v>
       </c>
       <c r="D7">
-        <v>106.7</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="E7">
-        <v>0.99417999999999995</v>
+        <v>0.99585999999999997</v>
       </c>
       <c r="H7" t="s">
+        <v>145</v>
+      </c>
+      <c r="I7" t="s">
+        <v>141</v>
+      </c>
+      <c r="J7">
+        <v>1.9336188418727293E-2</v>
+      </c>
+      <c r="K7" t="s">
         <v>142</v>
       </c>
-      <c r="I7" t="s">
-        <v>138</v>
-      </c>
-      <c r="J7">
-        <v>8.2169211344949131E-2</v>
-      </c>
-      <c r="K7" t="s">
-        <v>139</v>
-      </c>
       <c r="L7" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P7" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="Q7" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="R7" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U7" t="s">
         <v>112</v>
       </c>
       <c r="V7" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="W7" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="X7" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="2:33" x14ac:dyDescent="0.45">
@@ -2444,49 +2534,49 @@
         <v>120</v>
       </c>
       <c r="C8">
-        <v>0.49155601918804742</v>
+        <v>1.7874764334110815</v>
       </c>
       <c r="D8">
-        <v>97.9</v>
+        <v>107.80000000000001</v>
       </c>
       <c r="E8">
-        <v>0.99465999999999999</v>
+        <v>0.99412</v>
       </c>
       <c r="H8" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="I8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J8">
-        <v>1.9088325242681982E-2</v>
+        <v>7.9343495051634627E-2</v>
       </c>
       <c r="K8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P8" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="Q8" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="R8" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U8" t="s">
         <v>112</v>
       </c>
       <c r="V8" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="W8" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="X8" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="2:33" x14ac:dyDescent="0.45">
@@ -2497,46 +2587,46 @@
         <v>0.49155601918804742</v>
       </c>
       <c r="D9">
-        <v>191.4</v>
+        <v>50.6</v>
       </c>
       <c r="E9">
-        <v>0.98956</v>
+        <v>0.99724000000000002</v>
       </c>
       <c r="H9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J9">
-        <v>9.4209834080292085E-2</v>
+        <v>8.9281451287542654E-2</v>
       </c>
       <c r="K9" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Q9" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="R9" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U9" t="s">
         <v>112</v>
       </c>
       <c r="V9" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="W9" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="X9" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="2:33" x14ac:dyDescent="0.45">
@@ -2544,49 +2634,49 @@
         <v>122</v>
       </c>
       <c r="C10">
-        <v>3.7537005101632714</v>
+        <v>0.49155601918804742</v>
       </c>
       <c r="D10">
-        <v>124.30000000000001</v>
+        <v>191.4</v>
       </c>
       <c r="E10">
-        <v>0.99321999999999999</v>
+        <v>0.98956</v>
       </c>
       <c r="H10" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I10" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J10">
-        <v>0.14207203459557918</v>
+        <v>0.15551550087423788</v>
       </c>
       <c r="K10" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L10" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P10" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Q10" t="s">
+        <v>200</v>
+      </c>
+      <c r="R10" t="s">
+        <v>194</v>
+      </c>
+      <c r="U10" t="s">
+        <v>112</v>
+      </c>
+      <c r="V10" t="s">
+        <v>215</v>
+      </c>
+      <c r="W10" t="s">
         <v>193</v>
       </c>
-      <c r="R10" t="s">
-        <v>187</v>
-      </c>
-      <c r="U10" t="s">
-        <v>112</v>
-      </c>
-      <c r="V10" t="s">
-        <v>207</v>
-      </c>
-      <c r="W10" t="s">
-        <v>186</v>
-      </c>
       <c r="X10" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" spans="2:33" x14ac:dyDescent="0.45">
@@ -2594,49 +2684,49 @@
         <v>123</v>
       </c>
       <c r="C11">
-        <v>0.98311203837609484</v>
+        <v>1.7874764334110815</v>
       </c>
       <c r="D11">
-        <v>101.2</v>
+        <v>143</v>
       </c>
       <c r="E11">
-        <v>0.99448000000000003</v>
+        <v>0.99219999999999997</v>
       </c>
       <c r="H11" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I11" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J11">
-        <v>2.4619161264515566E-2</v>
+        <v>3.4902220059878364E-2</v>
       </c>
       <c r="K11" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L11" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P11" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q11" t="s">
+        <v>201</v>
+      </c>
+      <c r="R11" t="s">
         <v>194</v>
       </c>
-      <c r="R11" t="s">
-        <v>187</v>
-      </c>
       <c r="U11" t="s">
         <v>112</v>
       </c>
       <c r="V11" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="W11" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="X11" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="2:33" x14ac:dyDescent="0.45">
@@ -2644,49 +2734,49 @@
         <v>124</v>
       </c>
       <c r="C12">
-        <v>1.7874764334110815</v>
+        <v>0.49155601918804742</v>
       </c>
       <c r="D12">
-        <v>53.900000000000006</v>
+        <v>73.7</v>
       </c>
       <c r="E12">
-        <v>0.99705999999999995</v>
+        <v>0.99597999999999998</v>
       </c>
       <c r="H12" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I12" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J12">
-        <v>0.13535303803123419</v>
+        <v>6.3993351279734101E-2</v>
       </c>
       <c r="K12" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L12" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P12" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Q12" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="R12" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U12" t="s">
         <v>112</v>
       </c>
       <c r="V12" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="W12" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="X12" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" spans="2:33" x14ac:dyDescent="0.45">
@@ -2694,49 +2784,49 @@
         <v>125</v>
       </c>
       <c r="C13">
-        <v>0.98311203837609484</v>
+        <v>1.4746680575641422</v>
       </c>
       <c r="D13">
-        <v>92.4</v>
+        <v>50.6</v>
       </c>
       <c r="E13">
-        <v>0.99495999999999996</v>
+        <v>0.99724000000000002</v>
       </c>
       <c r="H13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="I13" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J13">
-        <v>3.9205245741864479E-2</v>
+        <v>2.0107359124674009E-2</v>
       </c>
       <c r="K13" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L13" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Q13" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="R13" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U13" t="s">
         <v>112</v>
       </c>
       <c r="V13" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="W13" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="X13" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" spans="2:33" x14ac:dyDescent="0.45">
@@ -2744,49 +2834,49 @@
         <v>126</v>
       </c>
       <c r="C14">
-        <v>2.2790324525991292</v>
+        <v>0.49155601918804742</v>
       </c>
       <c r="D14">
-        <v>46.2</v>
+        <v>67.100000000000009</v>
       </c>
       <c r="E14">
-        <v>0.99748000000000003</v>
+        <v>0.99634</v>
       </c>
       <c r="H14" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I14" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J14">
-        <v>0.15716430349956209</v>
+        <v>0.20048826891947633</v>
       </c>
       <c r="K14" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L14" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P14" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q14" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="R14" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U14" t="s">
         <v>112</v>
       </c>
       <c r="V14" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="W14" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="X14" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" spans="2:33" x14ac:dyDescent="0.45">
@@ -2794,49 +2884,49 @@
         <v>127</v>
       </c>
       <c r="C15">
-        <v>0.98311203837609484</v>
+        <v>0.49155601918804742</v>
       </c>
       <c r="D15">
-        <v>77</v>
+        <v>101.2</v>
       </c>
       <c r="E15">
-        <v>0.99580000000000002</v>
+        <v>0.99448000000000003</v>
       </c>
       <c r="H15" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I15" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J15">
-        <v>8.5256535804089525E-2</v>
+        <v>0.1376937968579082</v>
       </c>
       <c r="K15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L15" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P15" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q15" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="R15" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U15" t="s">
         <v>112</v>
       </c>
       <c r="V15" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="W15" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="X15" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16" spans="2:33" x14ac:dyDescent="0.45">
@@ -2844,49 +2934,49 @@
         <v>128</v>
       </c>
       <c r="C16">
-        <v>1.7874764334110815</v>
+        <v>2.2790324525991292</v>
       </c>
       <c r="D16">
-        <v>149.60000000000002</v>
+        <v>124.30000000000001</v>
       </c>
       <c r="E16">
-        <v>0.99184000000000005</v>
+        <v>0.99321999999999999</v>
       </c>
       <c r="H16" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="I16" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J16">
-        <v>0.20086231039523153</v>
+        <v>9.7710613758789755E-2</v>
       </c>
       <c r="K16" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L16" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P16" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q16" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="R16" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U16" t="s">
         <v>112</v>
       </c>
       <c r="V16" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="W16" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="X16" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.45">
@@ -2894,49 +2984,49 @@
         <v>129</v>
       </c>
       <c r="C17">
-        <v>1.7874764334110815</v>
+        <v>0.49155601918804742</v>
       </c>
       <c r="D17">
-        <v>95.7</v>
+        <v>105.60000000000001</v>
       </c>
       <c r="E17">
-        <v>0.99478</v>
+        <v>0.99424000000000001</v>
       </c>
       <c r="H17" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I17" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J17">
-        <v>8.2169211344949131E-2</v>
+        <v>8.1627754367396457E-2</v>
       </c>
       <c r="K17" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L17" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P17" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q17" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="R17" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U17" t="s">
         <v>112</v>
       </c>
       <c r="V17" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="W17" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="X17" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.45">
@@ -2947,46 +3037,46 @@
         <v>1.7874764334110815</v>
       </c>
       <c r="D18">
-        <v>143</v>
+        <v>53.900000000000006</v>
       </c>
       <c r="E18">
-        <v>0.99219999999999997</v>
+        <v>0.99705999999999995</v>
       </c>
       <c r="H18" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="I18" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J18">
-        <v>1.9088325242681982E-2</v>
+        <v>1.9336188418727293E-2</v>
       </c>
       <c r="K18" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L18" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P18" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q18" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="R18" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U18" t="s">
         <v>112</v>
       </c>
       <c r="V18" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="W18" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="X18" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.45">
@@ -2994,49 +3084,49 @@
         <v>131</v>
       </c>
       <c r="C19">
-        <v>0.49155601918804742</v>
+        <v>0.98311203837609484</v>
       </c>
       <c r="D19">
-        <v>105.60000000000001</v>
+        <v>92.4</v>
       </c>
       <c r="E19">
-        <v>0.99424000000000001</v>
+        <v>0.99495999999999996</v>
       </c>
       <c r="H19" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I19" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J19">
-        <v>9.4209834080292085E-2</v>
+        <v>7.9343495051634627E-2</v>
       </c>
       <c r="K19" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L19" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P19" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q19" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="R19" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U19" t="s">
         <v>112</v>
       </c>
       <c r="V19" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="W19" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="X19" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" spans="2:24" x14ac:dyDescent="0.45">
@@ -3044,2329 +3134,2521 @@
         <v>132</v>
       </c>
       <c r="C20">
-        <v>0.98311203837609484</v>
+        <v>2.2790324525991292</v>
       </c>
       <c r="D20">
-        <v>78.100000000000009</v>
+        <v>46.2</v>
       </c>
       <c r="E20">
-        <v>0.99573999999999996</v>
+        <v>0.99748000000000003</v>
       </c>
       <c r="H20" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="I20" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J20">
-        <v>0.14207203459557918</v>
+        <v>8.9281451287542654E-2</v>
       </c>
       <c r="K20" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L20" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P20" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q20" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="R20" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U20" t="s">
         <v>112</v>
       </c>
       <c r="V20" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="W20" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="X20" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="21" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21">
+        <v>0.49155601918804742</v>
+      </c>
+      <c r="D21">
+        <v>101.2</v>
+      </c>
+      <c r="E21">
+        <v>0.99448000000000003</v>
+      </c>
+      <c r="H21" t="s">
+        <v>159</v>
+      </c>
+      <c r="I21" t="s">
+        <v>141</v>
+      </c>
+      <c r="J21">
+        <v>0.15551550087423788</v>
+      </c>
+      <c r="K21" t="s">
+        <v>142</v>
+      </c>
+      <c r="L21" t="s">
+        <v>141</v>
+      </c>
+      <c r="P21" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>200</v>
+      </c>
+      <c r="R21" t="s">
+        <v>194</v>
+      </c>
+      <c r="U21" t="s">
+        <v>112</v>
+      </c>
+      <c r="V21" t="s">
+        <v>224</v>
+      </c>
+      <c r="W21" t="s">
+        <v>220</v>
+      </c>
+      <c r="X21" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="22" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>134</v>
+      </c>
+      <c r="C22">
+        <v>1.7874764334110815</v>
+      </c>
+      <c r="D22">
+        <v>149.60000000000002</v>
+      </c>
+      <c r="E22">
+        <v>0.99184000000000005</v>
+      </c>
+      <c r="H22" t="s">
+        <v>160</v>
+      </c>
+      <c r="I22" t="s">
+        <v>141</v>
+      </c>
+      <c r="J22">
+        <v>3.4902220059878364E-2</v>
+      </c>
+      <c r="K22" t="s">
+        <v>142</v>
+      </c>
+      <c r="L22" t="s">
+        <v>141</v>
+      </c>
+      <c r="P22" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q22" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="H21" t="s">
-        <v>156</v>
-      </c>
-      <c r="I21" t="s">
-        <v>138</v>
-      </c>
-      <c r="J21">
-        <v>2.4619161264515566E-2</v>
-      </c>
-      <c r="K21" t="s">
-        <v>139</v>
-      </c>
-      <c r="L21" t="s">
-        <v>138</v>
-      </c>
-      <c r="P21" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q21" t="s">
+      <c r="R22" t="s">
         <v>194</v>
       </c>
-      <c r="R21" t="s">
-        <v>187</v>
-      </c>
-      <c r="U21" t="s">
-        <v>112</v>
-      </c>
-      <c r="V21" t="s">
-        <v>216</v>
-      </c>
-      <c r="W21" t="s">
-        <v>212</v>
-      </c>
-      <c r="X21" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="H22" t="s">
-        <v>157</v>
-      </c>
-      <c r="I22" t="s">
-        <v>138</v>
-      </c>
-      <c r="J22">
-        <v>0.13535303803123419</v>
-      </c>
-      <c r="K22" t="s">
-        <v>139</v>
-      </c>
-      <c r="L22" t="s">
-        <v>138</v>
-      </c>
-      <c r="P22" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>195</v>
-      </c>
-      <c r="R22" t="s">
-        <v>187</v>
-      </c>
       <c r="U22" t="s">
         <v>112</v>
       </c>
       <c r="V22" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="W22" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="X22" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B23" t="s">
+        <v>135</v>
+      </c>
+      <c r="C23">
+        <v>2.2790324525991292</v>
+      </c>
+      <c r="D23">
+        <v>92.4</v>
+      </c>
+      <c r="E23">
+        <v>0.99495999999999996</v>
+      </c>
       <c r="H23" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I23" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J23">
-        <v>3.9205245741864479E-2</v>
+        <v>6.3993351279734101E-2</v>
       </c>
       <c r="K23" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L23" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P23" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q23" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="R23" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U23" t="s">
         <v>112</v>
       </c>
       <c r="V23" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="W23" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="X23" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.45">
       <c r="H24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="I24" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J24">
-        <v>0.15716430349956209</v>
+        <v>2.0107359124674009E-2</v>
       </c>
       <c r="K24" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L24" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q24" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="R24" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U24" t="s">
         <v>112</v>
       </c>
       <c r="V24" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="W24" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="X24" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.45">
       <c r="H25" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I25" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J25">
-        <v>8.5256535804089525E-2</v>
+        <v>0.20048826891947633</v>
       </c>
       <c r="K25" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L25" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P25" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Q25" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="R25" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U25" t="s">
         <v>112</v>
       </c>
       <c r="V25" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="W25" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="X25" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26" spans="2:24" x14ac:dyDescent="0.45">
       <c r="H26" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I26" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J26">
-        <v>0.20086231039523153</v>
+        <v>0.1376937968579082</v>
       </c>
       <c r="K26" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L26" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P26" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q26" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="R26" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U26" t="s">
         <v>112</v>
       </c>
       <c r="V26" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="W26" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="X26" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.45">
       <c r="H27" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I27" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J27">
-        <v>8.2169211344949131E-2</v>
+        <v>9.7710613758789755E-2</v>
       </c>
       <c r="K27" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L27" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P27" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q27" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="R27" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U27" t="s">
         <v>112</v>
       </c>
       <c r="V27" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="W27" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="X27" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.45">
       <c r="H28" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="I28" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J28">
-        <v>1.9088325242681982E-2</v>
+        <v>8.1627754367396457E-2</v>
       </c>
       <c r="K28" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L28" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P28" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q28" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="R28" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U28" t="s">
         <v>112</v>
       </c>
       <c r="V28" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="W28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="X28" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="29" spans="2:24" x14ac:dyDescent="0.45">
       <c r="H29" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I29" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J29">
-        <v>9.4209834080292085E-2</v>
+        <v>1.9336188418727293E-2</v>
       </c>
       <c r="K29" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L29" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P29" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q29" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="R29" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U29" t="s">
         <v>112</v>
       </c>
       <c r="V29" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="W29" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="X29" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="30" spans="2:24" x14ac:dyDescent="0.45">
       <c r="H30" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I30" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J30">
-        <v>0.14207203459557918</v>
+        <v>7.9343495051634627E-2</v>
       </c>
       <c r="K30" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L30" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P30" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q30" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="R30" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U30" t="s">
         <v>112</v>
       </c>
       <c r="V30" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="W30" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="X30" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.45">
       <c r="H31" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I31" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J31">
-        <v>2.4619161264515566E-2</v>
+        <v>8.9281451287542654E-2</v>
       </c>
       <c r="K31" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L31" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P31" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q31" t="s">
+        <v>199</v>
+      </c>
+      <c r="R31" t="s">
         <v>194</v>
       </c>
-      <c r="R31" t="s">
-        <v>187</v>
-      </c>
       <c r="U31" t="s">
         <v>112</v>
       </c>
       <c r="V31" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="W31" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="X31" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="32" spans="2:24" x14ac:dyDescent="0.45">
       <c r="H32" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I32" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J32">
-        <v>0.13535303803123419</v>
+        <v>0.15551550087423788</v>
       </c>
       <c r="K32" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L32" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P32" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q32" t="s">
+        <v>200</v>
+      </c>
+      <c r="R32" t="s">
+        <v>194</v>
+      </c>
+      <c r="U32" t="s">
+        <v>112</v>
+      </c>
+      <c r="V32" t="s">
+        <v>235</v>
+      </c>
+      <c r="W32" t="s">
         <v>195</v>
       </c>
-      <c r="R32" t="s">
-        <v>187</v>
-      </c>
-      <c r="U32" t="s">
-        <v>112</v>
-      </c>
-      <c r="V32" t="s">
-        <v>227</v>
-      </c>
-      <c r="W32" t="s">
-        <v>188</v>
-      </c>
       <c r="X32" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="33" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H33" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I33" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J33">
-        <v>3.9205245741864479E-2</v>
+        <v>3.4902220059878364E-2</v>
       </c>
       <c r="K33" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L33" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P33" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q33" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="R33" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U33" t="s">
         <v>112</v>
       </c>
       <c r="V33" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="W33" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="X33" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="34" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H34" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="I34" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J34">
-        <v>0.15716430349956209</v>
+        <v>6.3993351279734101E-2</v>
       </c>
       <c r="K34" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L34" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P34" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q34" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="R34" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U34" t="s">
         <v>112</v>
       </c>
       <c r="V34" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="W34" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="X34" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="35" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H35" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="I35" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J35">
-        <v>8.5256535804089525E-2</v>
+        <v>2.0107359124674009E-2</v>
       </c>
       <c r="K35" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L35" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P35" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q35" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="R35" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U35" t="s">
         <v>112</v>
       </c>
       <c r="V35" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="W35" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="X35" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="36" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H36" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I36" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J36">
-        <v>0.20086231039523153</v>
+        <v>0.20048826891947633</v>
       </c>
       <c r="K36" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L36" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P36" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q36" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="R36" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U36" t="s">
         <v>112</v>
       </c>
       <c r="V36" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="W36" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="X36" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="37" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H37" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I37" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J37">
-        <v>8.2169211344949131E-2</v>
+        <v>0.1376937968579082</v>
       </c>
       <c r="K37" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L37" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P37" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q37" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="R37" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U37" t="s">
         <v>112</v>
       </c>
       <c r="V37" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="W37" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="X37" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="38" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H38" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="I38" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J38">
-        <v>1.9088325242681982E-2</v>
+        <v>9.7710613758789755E-2</v>
       </c>
       <c r="K38" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L38" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P38" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q38" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="R38" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U38" t="s">
         <v>112</v>
       </c>
       <c r="V38" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="W38" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="X38" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="39" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H39" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I39" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J39">
-        <v>9.4209834080292085E-2</v>
+        <v>8.1627754367396457E-2</v>
       </c>
       <c r="K39" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L39" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P39" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q39" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="R39" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U39" t="s">
         <v>112</v>
       </c>
       <c r="V39" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="W39" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="X39" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="40" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H40" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="I40" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J40">
-        <v>0.14207203459557918</v>
+        <v>1.9336188418727293E-2</v>
       </c>
       <c r="K40" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L40" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P40" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q40" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="R40" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U40" t="s">
         <v>112</v>
       </c>
       <c r="V40" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="W40" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="X40" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="41" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H41" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I41" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J41">
-        <v>2.4619161264515566E-2</v>
+        <v>7.9343495051634627E-2</v>
       </c>
       <c r="K41" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L41" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P41" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q41" t="s">
+        <v>198</v>
+      </c>
+      <c r="R41" t="s">
         <v>194</v>
       </c>
-      <c r="R41" t="s">
-        <v>187</v>
-      </c>
       <c r="U41" t="s">
         <v>112</v>
       </c>
       <c r="V41" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="W41" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="X41" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="42" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H42" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="I42" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J42">
-        <v>0.13535303803123419</v>
+        <v>8.9281451287542654E-2</v>
       </c>
       <c r="K42" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L42" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P42" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q42" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="R42" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U42" t="s">
         <v>112</v>
       </c>
       <c r="V42" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="W42" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="X42" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="43" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H43" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="I43" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J43">
-        <v>3.9205245741864479E-2</v>
+        <v>0.15551550087423788</v>
       </c>
       <c r="K43" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L43" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P43" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q43" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="R43" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U43" t="s">
         <v>112</v>
       </c>
       <c r="V43" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="W43" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="X43" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="44" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H44" t="s">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="I44" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="J44">
-        <v>9.7999999999999893E-2</v>
+        <v>3.4902220059878364E-2</v>
       </c>
       <c r="K44" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L44" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="P44" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q44" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="R44" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U44" t="s">
         <v>112</v>
       </c>
       <c r="V44" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="W44" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="X44" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="45" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H45" t="s">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="I45" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="J45">
-        <v>9.7999999999999893E-2</v>
+        <v>6.3993351279734101E-2</v>
       </c>
       <c r="K45" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L45" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="P45" t="s">
         <v>183</v>
       </c>
       <c r="Q45" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="R45" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="U45" t="s">
         <v>112</v>
       </c>
       <c r="V45" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="W45" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="X45" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="46" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H46" t="s">
+        <v>184</v>
+      </c>
+      <c r="I46" t="s">
         <v>141</v>
       </c>
-      <c r="I46" t="s">
-        <v>179</v>
-      </c>
       <c r="J46">
-        <v>9.7999999999999893E-2</v>
+        <v>2.0107359124674009E-2</v>
       </c>
       <c r="K46" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L46" t="s">
-        <v>179</v>
+        <v>141</v>
+      </c>
+      <c r="P46" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>203</v>
+      </c>
+      <c r="R46" t="s">
+        <v>194</v>
       </c>
       <c r="U46" t="s">
         <v>112</v>
       </c>
       <c r="V46" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="W46" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="X46" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="47" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H47" t="s">
+        <v>185</v>
+      </c>
+      <c r="I47" t="s">
+        <v>141</v>
+      </c>
+      <c r="J47">
+        <v>0.20048826891947633</v>
+      </c>
+      <c r="K47" t="s">
         <v>142</v>
       </c>
-      <c r="I47" t="s">
-        <v>179</v>
-      </c>
-      <c r="J47">
-        <v>9.7999999999999893E-2</v>
-      </c>
-      <c r="K47" t="s">
-        <v>139</v>
-      </c>
       <c r="L47" t="s">
-        <v>179</v>
+        <v>141</v>
+      </c>
+      <c r="P47" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>204</v>
+      </c>
+      <c r="R47" t="s">
+        <v>194</v>
       </c>
       <c r="U47" t="s">
         <v>112</v>
       </c>
       <c r="V47" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="W47" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="X47" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="48" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H48" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I48" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J48">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K48" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L48" t="s">
-        <v>179</v>
+        <v>186</v>
+      </c>
+      <c r="P48" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>205</v>
+      </c>
+      <c r="R48" t="s">
+        <v>194</v>
       </c>
       <c r="U48" t="s">
         <v>112</v>
       </c>
       <c r="V48" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="W48" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="X48" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="49" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H49" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I49" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J49">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K49" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L49" t="s">
-        <v>179</v>
+        <v>186</v>
+      </c>
+      <c r="P49" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>206</v>
+      </c>
+      <c r="R49" t="s">
+        <v>194</v>
       </c>
       <c r="U49" t="s">
         <v>112</v>
       </c>
       <c r="V49" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="W49" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="X49" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="50" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H50" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I50" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J50">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K50" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L50" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U50" t="s">
         <v>112</v>
       </c>
       <c r="V50" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="W50" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="X50" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="51" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I51" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J51">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K51" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L51" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U51" t="s">
         <v>112</v>
       </c>
       <c r="V51" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="W51" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="X51" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="52" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H52" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I52" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J52">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K52" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L52" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U52" t="s">
         <v>112</v>
       </c>
       <c r="V52" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="W52" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="X52" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="53" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H53" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I53" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J53">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K53" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L53" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U53" t="s">
         <v>112</v>
       </c>
       <c r="V53" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="W53" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="X53" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="54" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H54" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I54" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J54">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K54" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L54" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U54" t="s">
         <v>112</v>
       </c>
       <c r="V54" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="W54" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="X54" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="55" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H55" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I55" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J55">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K55" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L55" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U55" t="s">
         <v>112</v>
       </c>
       <c r="V55" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="W55" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="X55" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="56" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H56" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I56" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J56">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K56" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L56" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U56" t="s">
         <v>112</v>
       </c>
       <c r="V56" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="W56" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="X56" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="57" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H57" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I57" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J57">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K57" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L57" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U57" t="s">
         <v>112</v>
       </c>
       <c r="V57" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="W57" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="X57" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="58" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H58" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I58" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J58">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K58" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L58" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U58" t="s">
         <v>112</v>
       </c>
       <c r="V58" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="W58" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="X58" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="59" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I59" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J59">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K59" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L59" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U59" t="s">
         <v>112</v>
       </c>
       <c r="V59" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="W59" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="X59" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="60" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H60" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I60" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J60">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K60" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L60" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U60" t="s">
         <v>112</v>
       </c>
       <c r="V60" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="W60" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="X60" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="61" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H61" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I61" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J61">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K61" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L61" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U61" t="s">
         <v>112</v>
       </c>
       <c r="V61" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="W61" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="X61" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="62" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H62" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I62" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J62">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K62" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L62" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U62" t="s">
         <v>112</v>
       </c>
       <c r="V62" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="W62" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="X62" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="63" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H63" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I63" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J63">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K63" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L63" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U63" t="s">
         <v>112</v>
       </c>
       <c r="V63" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="W63" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="X63" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="64" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H64" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I64" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J64">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K64" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L64" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U64" t="s">
         <v>112</v>
       </c>
       <c r="V64" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="W64" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="X64" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H65" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I65" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J65">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K65" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L65" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U65" t="s">
         <v>112</v>
       </c>
       <c r="V65" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="W65" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="X65" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="66" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H66" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I66" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J66">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K66" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L66" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U66" t="s">
         <v>112</v>
       </c>
       <c r="V66" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="W66" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="X66" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="67" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H67" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I67" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J67">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K67" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L67" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U67" t="s">
         <v>112</v>
       </c>
       <c r="V67" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="W67" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="X67" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="68" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H68" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I68" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J68">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K68" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L68" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U68" t="s">
         <v>112</v>
       </c>
       <c r="V68" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="W68" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="X68" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="69" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H69" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I69" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J69">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K69" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L69" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U69" t="s">
         <v>112</v>
       </c>
       <c r="V69" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="W69" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="X69" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="70" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H70" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I70" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J70">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K70" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L70" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U70" t="s">
         <v>112</v>
       </c>
       <c r="V70" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="W70" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="X70" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="71" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H71" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I71" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J71">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K71" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L71" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U71" t="s">
         <v>112</v>
       </c>
       <c r="V71" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="W71" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="X71" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="72" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H72" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I72" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J72">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K72" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L72" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U72" t="s">
         <v>112</v>
       </c>
       <c r="V72" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="W72" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="X72" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="73" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H73" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I73" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J73">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K73" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L73" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U73" t="s">
         <v>112</v>
       </c>
       <c r="V73" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="W73" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="X73" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="74" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H74" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I74" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J74">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K74" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L74" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U74" t="s">
         <v>112</v>
       </c>
       <c r="V74" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="W74" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="X74" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="75" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H75" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I75" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J75">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K75" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L75" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U75" t="s">
         <v>112</v>
       </c>
       <c r="V75" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="W75" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="X75" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H76" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I76" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J76">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K76" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L76" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U76" t="s">
         <v>112</v>
       </c>
       <c r="V76" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="W76" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="X76" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="77" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H77" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I77" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J77">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K77" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L77" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U77" t="s">
         <v>112</v>
       </c>
       <c r="V77" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="W77" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="X77" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="78" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H78" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I78" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J78">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K78" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L78" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U78" t="s">
         <v>112</v>
       </c>
       <c r="V78" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="W78" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="X78" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="79" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H79" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I79" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J79">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K79" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L79" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U79" t="s">
         <v>112</v>
       </c>
       <c r="V79" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="W79" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="X79" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="80" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I80" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J80">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K80" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L80" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U80" t="s">
         <v>112</v>
       </c>
       <c r="V80" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="W80" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="X80" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="81" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H81" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I81" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J81">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K81" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L81" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U81" t="s">
         <v>112</v>
       </c>
       <c r="V81" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="W81" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="X81" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="82" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H82" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I82" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J82">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K82" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L82" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U82" t="s">
         <v>112</v>
       </c>
       <c r="V82" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="W82" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="X82" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="83" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H83" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I83" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J83">
-        <v>9.7999999999999893E-2</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K83" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L83" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="U83" t="s">
         <v>112</v>
       </c>
       <c r="V83" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="W83" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="X83" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="84" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H84" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I84" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="J84">
-        <v>0.35949113888257112</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K84" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L84" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="U84" t="s">
         <v>112</v>
       </c>
       <c r="V84" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="W84" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="X84" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="85" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H85" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I85" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="J85">
-        <v>0.37058823529411761</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K85" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L85" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="U85" t="s">
         <v>112</v>
       </c>
       <c r="V85" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="W85" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="X85" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="86" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H86" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I86" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="J86">
-        <v>0.62050886111742887</v>
+        <v>8.9090909090909082E-2</v>
       </c>
       <c r="K86" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L86" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="U86" t="s">
         <v>112</v>
       </c>
       <c r="V86" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="W86" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="X86" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="87" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H87" t="s">
+        <v>181</v>
+      </c>
+      <c r="I87" t="s">
+        <v>186</v>
+      </c>
+      <c r="J87">
+        <v>8.9090909090909082E-2</v>
+      </c>
+      <c r="K87" t="s">
+        <v>142</v>
+      </c>
+      <c r="L87" t="s">
+        <v>186</v>
+      </c>
+      <c r="U87" t="s">
+        <v>112</v>
+      </c>
+      <c r="V87" t="s">
+        <v>284</v>
+      </c>
+      <c r="W87" t="s">
+        <v>198</v>
+      </c>
+      <c r="X87" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="88" spans="8:24" x14ac:dyDescent="0.45">
+      <c r="H88" t="s">
+        <v>182</v>
+      </c>
+      <c r="I88" t="s">
+        <v>186</v>
+      </c>
+      <c r="J88">
+        <v>8.9090909090909082E-2</v>
+      </c>
+      <c r="K88" t="s">
+        <v>142</v>
+      </c>
+      <c r="L88" t="s">
+        <v>186</v>
+      </c>
+      <c r="U88" t="s">
+        <v>112</v>
+      </c>
+      <c r="V88" t="s">
+        <v>285</v>
+      </c>
+      <c r="W88" t="s">
+        <v>198</v>
+      </c>
+      <c r="X88" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="89" spans="8:24" x14ac:dyDescent="0.45">
+      <c r="H89" t="s">
         <v>183</v>
       </c>
-      <c r="I87" t="s">
-        <v>182</v>
-      </c>
-      <c r="J87">
-        <v>0.60941176470588243</v>
-      </c>
-      <c r="K87" t="s">
-        <v>139</v>
-      </c>
-      <c r="L87" t="s">
-        <v>182</v>
-      </c>
-      <c r="U87" t="s">
-        <v>112</v>
-      </c>
-      <c r="V87" t="s">
-        <v>276</v>
-      </c>
-      <c r="W87" t="s">
-        <v>191</v>
-      </c>
-      <c r="X87" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="88" spans="8:24" x14ac:dyDescent="0.45">
-      <c r="U88" t="s">
-        <v>112</v>
-      </c>
-      <c r="V88" t="s">
-        <v>277</v>
-      </c>
-      <c r="W88" t="s">
-        <v>191</v>
-      </c>
-      <c r="X88" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="89" spans="8:24" x14ac:dyDescent="0.45">
+      <c r="I89" t="s">
+        <v>186</v>
+      </c>
+      <c r="J89">
+        <v>8.9090909090909082E-2</v>
+      </c>
+      <c r="K89" t="s">
+        <v>142</v>
+      </c>
+      <c r="L89" t="s">
+        <v>186</v>
+      </c>
       <c r="U89" t="s">
         <v>112</v>
       </c>
       <c r="V89" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="W89" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="X89" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="90" spans="8:24" x14ac:dyDescent="0.45">
+      <c r="H90" t="s">
+        <v>184</v>
+      </c>
+      <c r="I90" t="s">
+        <v>186</v>
+      </c>
+      <c r="J90">
+        <v>8.9090909090909082E-2</v>
+      </c>
+      <c r="K90" t="s">
+        <v>142</v>
+      </c>
+      <c r="L90" t="s">
+        <v>186</v>
+      </c>
       <c r="U90" t="s">
         <v>112</v>
       </c>
       <c r="V90" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="W90" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="X90" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="91" spans="8:24" x14ac:dyDescent="0.45">
+      <c r="H91" t="s">
+        <v>185</v>
+      </c>
+      <c r="I91" t="s">
+        <v>186</v>
+      </c>
+      <c r="J91">
+        <v>8.9090909090909082E-2</v>
+      </c>
+      <c r="K91" t="s">
+        <v>142</v>
+      </c>
+      <c r="L91" t="s">
+        <v>186</v>
+      </c>
       <c r="U91" t="s">
         <v>112</v>
       </c>
       <c r="V91" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="W91" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="X91" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="92" spans="8:24" x14ac:dyDescent="0.45">
+      <c r="H92" t="s">
+        <v>187</v>
+      </c>
+      <c r="I92" t="s">
+        <v>188</v>
+      </c>
+      <c r="J92">
+        <v>0.43066153624481801</v>
+      </c>
+      <c r="K92" t="s">
+        <v>142</v>
+      </c>
+      <c r="L92" t="s">
+        <v>188</v>
+      </c>
       <c r="U92" t="s">
         <v>112</v>
       </c>
       <c r="V92" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="W92" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="X92" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="93" spans="8:24" x14ac:dyDescent="0.45">
+      <c r="H93" t="s">
+        <v>187</v>
+      </c>
+      <c r="I93" t="s">
+        <v>189</v>
+      </c>
+      <c r="J93">
+        <v>0.37058823529411761</v>
+      </c>
+      <c r="K93" t="s">
+        <v>142</v>
+      </c>
+      <c r="L93" t="s">
+        <v>189</v>
+      </c>
       <c r="U93" t="s">
         <v>112</v>
       </c>
       <c r="V93" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="W93" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="X93" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="94" spans="8:24" x14ac:dyDescent="0.45">
+      <c r="H94" t="s">
+        <v>190</v>
+      </c>
+      <c r="I94" t="s">
+        <v>188</v>
+      </c>
+      <c r="J94">
+        <v>0.54933846375518192</v>
+      </c>
+      <c r="K94" t="s">
+        <v>142</v>
+      </c>
+      <c r="L94" t="s">
+        <v>188</v>
+      </c>
       <c r="U94" t="s">
         <v>112</v>
       </c>
       <c r="V94" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="W94" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="X94" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="95" spans="8:24" x14ac:dyDescent="0.45">
+      <c r="H95" t="s">
+        <v>190</v>
+      </c>
+      <c r="I95" t="s">
+        <v>189</v>
+      </c>
+      <c r="J95">
+        <v>0.60941176470588232</v>
+      </c>
+      <c r="K95" t="s">
+        <v>142</v>
+      </c>
+      <c r="L95" t="s">
+        <v>189</v>
+      </c>
       <c r="U95" t="s">
         <v>112</v>
       </c>
       <c r="V95" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="W95" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="X95" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="96" spans="8:24" x14ac:dyDescent="0.45">
@@ -5374,13 +5656,13 @@
         <v>112</v>
       </c>
       <c r="V96" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="W96" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="X96" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="97" spans="21:24" x14ac:dyDescent="0.45">
@@ -5388,13 +5670,13 @@
         <v>112</v>
       </c>
       <c r="V97" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="W97" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="X97" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="98" spans="21:24" x14ac:dyDescent="0.45">
@@ -5402,13 +5684,13 @@
         <v>112</v>
       </c>
       <c r="V98" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="W98" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="X98" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="99" spans="21:24" x14ac:dyDescent="0.45">
@@ -5416,13 +5698,13 @@
         <v>112</v>
       </c>
       <c r="V99" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="W99" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="X99" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="100" spans="21:24" x14ac:dyDescent="0.45">
@@ -5430,13 +5712,13 @@
         <v>112</v>
       </c>
       <c r="V100" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="W100" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="X100" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="101" spans="21:24" x14ac:dyDescent="0.45">
@@ -5444,13 +5726,13 @@
         <v>112</v>
       </c>
       <c r="V101" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="W101" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="X101" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="102" spans="21:24" x14ac:dyDescent="0.45">
@@ -5458,13 +5740,13 @@
         <v>112</v>
       </c>
       <c r="V102" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="W102" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="X102" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="103" spans="21:24" x14ac:dyDescent="0.45">
@@ -5472,13 +5754,13 @@
         <v>112</v>
       </c>
       <c r="V103" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="W103" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="X103" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="104" spans="21:24" x14ac:dyDescent="0.45">
@@ -5486,13 +5768,13 @@
         <v>112</v>
       </c>
       <c r="V104" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="W104" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="X104" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="105" spans="21:24" x14ac:dyDescent="0.45">
@@ -5500,13 +5782,13 @@
         <v>112</v>
       </c>
       <c r="V105" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="W105" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="X105" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="106" spans="21:24" x14ac:dyDescent="0.45">
@@ -5514,13 +5796,13 @@
         <v>112</v>
       </c>
       <c r="V106" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="W106" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="X106" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="107" spans="21:24" x14ac:dyDescent="0.45">
@@ -5528,13 +5810,13 @@
         <v>112</v>
       </c>
       <c r="V107" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="W107" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="X107" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="108" spans="21:24" x14ac:dyDescent="0.45">
@@ -5542,13 +5824,13 @@
         <v>112</v>
       </c>
       <c r="V108" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="W108" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="X108" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="109" spans="21:24" x14ac:dyDescent="0.45">
@@ -5556,13 +5838,13 @@
         <v>112</v>
       </c>
       <c r="V109" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="W109" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="X109" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="110" spans="21:24" x14ac:dyDescent="0.45">
@@ -5570,13 +5852,13 @@
         <v>112</v>
       </c>
       <c r="V110" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="W110" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="X110" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="111" spans="21:24" x14ac:dyDescent="0.45">
@@ -5584,13 +5866,13 @@
         <v>112</v>
       </c>
       <c r="V111" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="W111" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="X111" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="112" spans="21:24" x14ac:dyDescent="0.45">
@@ -5598,13 +5880,13 @@
         <v>112</v>
       </c>
       <c r="V112" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="W112" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="X112" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="113" spans="21:24" x14ac:dyDescent="0.45">
@@ -5612,13 +5894,13 @@
         <v>112</v>
       </c>
       <c r="V113" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="W113" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="X113" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="114" spans="21:24" x14ac:dyDescent="0.45">
@@ -5626,13 +5908,13 @@
         <v>112</v>
       </c>
       <c r="V114" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="W114" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="X114" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="115" spans="21:24" x14ac:dyDescent="0.45">
@@ -5640,13 +5922,13 @@
         <v>112</v>
       </c>
       <c r="V115" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="W115" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="X115" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="116" spans="21:24" x14ac:dyDescent="0.45">
@@ -5654,13 +5936,13 @@
         <v>112</v>
       </c>
       <c r="V116" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="W116" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="X116" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="117" spans="21:24" x14ac:dyDescent="0.45">
@@ -5668,13 +5950,13 @@
         <v>112</v>
       </c>
       <c r="V117" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="W117" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="X117" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="118" spans="21:24" x14ac:dyDescent="0.45">
@@ -5682,13 +5964,13 @@
         <v>112</v>
       </c>
       <c r="V118" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="W118" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="X118" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="119" spans="21:24" x14ac:dyDescent="0.45">
@@ -5696,13 +5978,13 @@
         <v>112</v>
       </c>
       <c r="V119" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="W119" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="X119" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="120" spans="21:24" x14ac:dyDescent="0.45">
@@ -5710,13 +5992,13 @@
         <v>112</v>
       </c>
       <c r="V120" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="W120" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="X120" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="121" spans="21:24" x14ac:dyDescent="0.45">
@@ -5724,13 +6006,13 @@
         <v>112</v>
       </c>
       <c r="V121" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="W121" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="X121" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="122" spans="21:24" x14ac:dyDescent="0.45">
@@ -5738,13 +6020,13 @@
         <v>112</v>
       </c>
       <c r="V122" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="W122" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="X122" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="123" spans="21:24" x14ac:dyDescent="0.45">
@@ -5752,13 +6034,13 @@
         <v>112</v>
       </c>
       <c r="V123" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="W123" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="X123" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="124" spans="21:24" x14ac:dyDescent="0.45">
@@ -5766,13 +6048,13 @@
         <v>112</v>
       </c>
       <c r="V124" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="W124" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="X124" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="125" spans="21:24" x14ac:dyDescent="0.45">
@@ -5780,13 +6062,13 @@
         <v>112</v>
       </c>
       <c r="V125" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="W125" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="X125" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="126" spans="21:24" x14ac:dyDescent="0.45">
@@ -5794,13 +6076,13 @@
         <v>112</v>
       </c>
       <c r="V126" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="W126" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="X126" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="127" spans="21:24" x14ac:dyDescent="0.45">
@@ -5808,13 +6090,13 @@
         <v>112</v>
       </c>
       <c r="V127" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="W127" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="X127" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="128" spans="21:24" x14ac:dyDescent="0.45">
@@ -5822,13 +6104,13 @@
         <v>112</v>
       </c>
       <c r="V128" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="W128" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="X128" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="129" spans="21:24" x14ac:dyDescent="0.45">
@@ -5836,13 +6118,13 @@
         <v>112</v>
       </c>
       <c r="V129" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="W129" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="X129" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="130" spans="21:24" x14ac:dyDescent="0.45">
@@ -5850,13 +6132,13 @@
         <v>112</v>
       </c>
       <c r="V130" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="W130" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="X130" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="131" spans="21:24" x14ac:dyDescent="0.45">
@@ -5864,13 +6146,13 @@
         <v>112</v>
       </c>
       <c r="V131" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="W131" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="X131" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="132" spans="21:24" x14ac:dyDescent="0.45">
@@ -5878,13 +6160,13 @@
         <v>112</v>
       </c>
       <c r="V132" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="W132" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="X132" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="133" spans="21:24" x14ac:dyDescent="0.45">
@@ -5892,13 +6174,13 @@
         <v>112</v>
       </c>
       <c r="V133" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="W133" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="X133" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="134" spans="21:24" x14ac:dyDescent="0.45">
@@ -5906,13 +6188,13 @@
         <v>112</v>
       </c>
       <c r="V134" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="W134" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="X134" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="135" spans="21:24" x14ac:dyDescent="0.45">
@@ -5920,13 +6202,13 @@
         <v>112</v>
       </c>
       <c r="V135" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="W135" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="X135" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="136" spans="21:24" x14ac:dyDescent="0.45">
@@ -5934,13 +6216,13 @@
         <v>112</v>
       </c>
       <c r="V136" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="W136" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="X136" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="137" spans="21:24" x14ac:dyDescent="0.45">
@@ -5948,13 +6230,13 @@
         <v>112</v>
       </c>
       <c r="V137" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="W137" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="X137" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="138" spans="21:24" x14ac:dyDescent="0.45">
@@ -5962,13 +6244,13 @@
         <v>112</v>
       </c>
       <c r="V138" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="W138" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="X138" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="139" spans="21:24" x14ac:dyDescent="0.45">
@@ -5976,13 +6258,13 @@
         <v>112</v>
       </c>
       <c r="V139" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="W139" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="X139" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="140" spans="21:24" x14ac:dyDescent="0.45">
@@ -5990,13 +6272,13 @@
         <v>112</v>
       </c>
       <c r="V140" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="W140" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="X140" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="141" spans="21:24" x14ac:dyDescent="0.45">
@@ -6004,13 +6286,13 @@
         <v>112</v>
       </c>
       <c r="V141" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="W141" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="X141" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="142" spans="21:24" x14ac:dyDescent="0.45">
@@ -6018,13 +6300,13 @@
         <v>112</v>
       </c>
       <c r="V142" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="W142" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="X142" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="143" spans="21:24" x14ac:dyDescent="0.45">
@@ -6032,13 +6314,13 @@
         <v>112</v>
       </c>
       <c r="V143" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="W143" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="X143" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="144" spans="21:24" x14ac:dyDescent="0.45">
@@ -6046,13 +6328,13 @@
         <v>112</v>
       </c>
       <c r="V144" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="W144" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="X144" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="145" spans="21:24" x14ac:dyDescent="0.45">
@@ -6060,13 +6342,13 @@
         <v>112</v>
       </c>
       <c r="V145" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="W145" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="X145" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="146" spans="21:24" x14ac:dyDescent="0.45">
@@ -6074,13 +6356,13 @@
         <v>112</v>
       </c>
       <c r="V146" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="W146" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="X146" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="147" spans="21:24" x14ac:dyDescent="0.45">
@@ -6088,13 +6370,13 @@
         <v>112</v>
       </c>
       <c r="V147" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="W147" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="X147" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="148" spans="21:24" x14ac:dyDescent="0.45">
@@ -6102,13 +6384,13 @@
         <v>112</v>
       </c>
       <c r="V148" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="W148" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="X148" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="149" spans="21:24" x14ac:dyDescent="0.45">
@@ -6116,13 +6398,13 @@
         <v>112</v>
       </c>
       <c r="V149" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="W149" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="X149" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="150" spans="21:24" x14ac:dyDescent="0.45">
@@ -6130,13 +6412,13 @@
         <v>112</v>
       </c>
       <c r="V150" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="W150" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="X150" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="151" spans="21:24" x14ac:dyDescent="0.45">
@@ -6144,13 +6426,13 @@
         <v>112</v>
       </c>
       <c r="V151" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="W151" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="X151" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="152" spans="21:24" x14ac:dyDescent="0.45">
@@ -6158,13 +6440,13 @@
         <v>112</v>
       </c>
       <c r="V152" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="W152" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="X152" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="153" spans="21:24" x14ac:dyDescent="0.45">
@@ -6172,13 +6454,13 @@
         <v>112</v>
       </c>
       <c r="V153" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="W153" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="X153" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="154" spans="21:24" x14ac:dyDescent="0.45">
@@ -6186,13 +6468,13 @@
         <v>112</v>
       </c>
       <c r="V154" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="W154" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="X154" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="155" spans="21:24" x14ac:dyDescent="0.45">
@@ -6200,13 +6482,13 @@
         <v>112</v>
       </c>
       <c r="V155" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="W155" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="X155" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="156" spans="21:24" x14ac:dyDescent="0.45">
@@ -6214,13 +6496,13 @@
         <v>112</v>
       </c>
       <c r="V156" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="W156" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="X156" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="157" spans="21:24" x14ac:dyDescent="0.45">
@@ -6228,13 +6510,13 @@
         <v>112</v>
       </c>
       <c r="V157" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="W157" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="X157" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="158" spans="21:24" x14ac:dyDescent="0.45">
@@ -6242,13 +6524,13 @@
         <v>112</v>
       </c>
       <c r="V158" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="W158" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="X158" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="159" spans="21:24" x14ac:dyDescent="0.45">
@@ -6256,13 +6538,13 @@
         <v>112</v>
       </c>
       <c r="V159" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="W159" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="X159" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="160" spans="21:24" x14ac:dyDescent="0.45">
@@ -6270,13 +6552,13 @@
         <v>112</v>
       </c>
       <c r="V160" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="W160" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="X160" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="161" spans="21:24" x14ac:dyDescent="0.45">
@@ -6284,13 +6566,13 @@
         <v>112</v>
       </c>
       <c r="V161" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="W161" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="X161" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="162" spans="21:24" x14ac:dyDescent="0.45">
@@ -6298,13 +6580,13 @@
         <v>112</v>
       </c>
       <c r="V162" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="W162" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="X162" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="163" spans="21:24" x14ac:dyDescent="0.45">
@@ -6312,13 +6594,13 @@
         <v>112</v>
       </c>
       <c r="V163" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="W163" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="X163" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="164" spans="21:24" x14ac:dyDescent="0.45">
@@ -6326,13 +6608,13 @@
         <v>112</v>
       </c>
       <c r="V164" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="W164" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="X164" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="165" spans="21:24" x14ac:dyDescent="0.45">
@@ -6340,13 +6622,13 @@
         <v>112</v>
       </c>
       <c r="V165" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="W165" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="X165" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="166" spans="21:24" x14ac:dyDescent="0.45">
@@ -6354,13 +6636,13 @@
         <v>112</v>
       </c>
       <c r="V166" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="W166" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="X166" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="167" spans="21:24" x14ac:dyDescent="0.45">
@@ -6368,13 +6650,13 @@
         <v>112</v>
       </c>
       <c r="V167" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="W167" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="X167" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="168" spans="21:24" x14ac:dyDescent="0.45">
@@ -6382,13 +6664,13 @@
         <v>112</v>
       </c>
       <c r="V168" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="W168" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="X168" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="169" spans="21:24" x14ac:dyDescent="0.45">
@@ -6396,13 +6678,13 @@
         <v>112</v>
       </c>
       <c r="V169" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="W169" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="X169" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="170" spans="21:24" x14ac:dyDescent="0.45">
@@ -6410,13 +6692,13 @@
         <v>112</v>
       </c>
       <c r="V170" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="W170" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="X170" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="171" spans="21:24" x14ac:dyDescent="0.45">
@@ -6424,13 +6706,13 @@
         <v>112</v>
       </c>
       <c r="V171" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="W171" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="X171" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="172" spans="21:24" x14ac:dyDescent="0.45">
@@ -6438,13 +6720,13 @@
         <v>112</v>
       </c>
       <c r="V172" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="W172" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="X172" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="173" spans="21:24" x14ac:dyDescent="0.45">
@@ -6452,13 +6734,13 @@
         <v>112</v>
       </c>
       <c r="V173" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="W173" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="X173" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="174" spans="21:24" x14ac:dyDescent="0.45">
@@ -6466,13 +6748,13 @@
         <v>112</v>
       </c>
       <c r="V174" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="W174" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="X174" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="175" spans="21:24" x14ac:dyDescent="0.45">
@@ -6480,13 +6762,13 @@
         <v>112</v>
       </c>
       <c r="V175" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="W175" t="s">
-        <v>197</v>
+        <v>363</v>
       </c>
       <c r="X175" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="176" spans="21:24" x14ac:dyDescent="0.45">
@@ -6494,13 +6776,13 @@
         <v>112</v>
       </c>
       <c r="V176" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="W176" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="X176" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="177" spans="21:24" x14ac:dyDescent="0.45">
@@ -6508,13 +6790,13 @@
         <v>112</v>
       </c>
       <c r="V177" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="W177" t="s">
-        <v>197</v>
+        <v>363</v>
       </c>
       <c r="X177" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="178" spans="21:24" x14ac:dyDescent="0.45">
@@ -6522,13 +6804,13 @@
         <v>112</v>
       </c>
       <c r="V178" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="W178" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="X178" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="179" spans="21:24" x14ac:dyDescent="0.45">
@@ -6536,13 +6818,13 @@
         <v>112</v>
       </c>
       <c r="V179" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="W179" t="s">
-        <v>197</v>
+        <v>363</v>
       </c>
       <c r="X179" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="180" spans="21:24" x14ac:dyDescent="0.45">
@@ -6550,13 +6832,13 @@
         <v>112</v>
       </c>
       <c r="V180" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="W180" t="s">
-        <v>197</v>
+        <v>363</v>
       </c>
       <c r="X180" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="181" spans="21:24" x14ac:dyDescent="0.45">
@@ -6564,13 +6846,13 @@
         <v>112</v>
       </c>
       <c r="V181" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="W181" t="s">
-        <v>197</v>
+        <v>363</v>
       </c>
       <c r="X181" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="182" spans="21:24" x14ac:dyDescent="0.45">
@@ -6578,13 +6860,13 @@
         <v>112</v>
       </c>
       <c r="V182" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="W182" t="s">
-        <v>197</v>
+        <v>363</v>
       </c>
       <c r="X182" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="183" spans="21:24" x14ac:dyDescent="0.45">
@@ -6592,13 +6874,13 @@
         <v>112</v>
       </c>
       <c r="V183" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="W183" t="s">
-        <v>197</v>
+        <v>363</v>
       </c>
       <c r="X183" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="184" spans="21:24" x14ac:dyDescent="0.45">
@@ -6606,13 +6888,13 @@
         <v>112</v>
       </c>
       <c r="V184" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="W184" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="X184" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="185" spans="21:24" x14ac:dyDescent="0.45">
@@ -6620,13 +6902,13 @@
         <v>112</v>
       </c>
       <c r="V185" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="W185" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="X185" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="186" spans="21:24" x14ac:dyDescent="0.45">
@@ -6634,13 +6916,13 @@
         <v>112</v>
       </c>
       <c r="V186" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="W186" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="X186" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="187" spans="21:24" x14ac:dyDescent="0.45">
@@ -6648,13 +6930,13 @@
         <v>112</v>
       </c>
       <c r="V187" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="W187" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="X187" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="188" spans="21:24" x14ac:dyDescent="0.45">
@@ -6662,13 +6944,13 @@
         <v>112</v>
       </c>
       <c r="V188" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="W188" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="X188" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="189" spans="21:24" x14ac:dyDescent="0.45">
@@ -6676,13 +6958,13 @@
         <v>112</v>
       </c>
       <c r="V189" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="W189" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="X189" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="190" spans="21:24" x14ac:dyDescent="0.45">
@@ -6690,13 +6972,13 @@
         <v>112</v>
       </c>
       <c r="V190" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="W190" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="X190" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="191" spans="21:24" x14ac:dyDescent="0.45">
@@ -6704,13 +6986,13 @@
         <v>112</v>
       </c>
       <c r="V191" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="W191" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="X191" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="192" spans="21:24" x14ac:dyDescent="0.45">
@@ -6718,13 +7000,13 @@
         <v>112</v>
       </c>
       <c r="V192" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="W192" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="X192" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="193" spans="21:24" x14ac:dyDescent="0.45">
@@ -6732,13 +7014,13 @@
         <v>112</v>
       </c>
       <c r="V193" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="W193" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="X193" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="194" spans="21:24" x14ac:dyDescent="0.45">
@@ -6746,13 +7028,13 @@
         <v>112</v>
       </c>
       <c r="V194" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="W194" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="X194" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="195" spans="21:24" x14ac:dyDescent="0.45">
@@ -6760,13 +7042,13 @@
         <v>112</v>
       </c>
       <c r="V195" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="W195" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="X195" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="196" spans="21:24" x14ac:dyDescent="0.45">
@@ -6774,13 +7056,13 @@
         <v>112</v>
       </c>
       <c r="V196" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="W196" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="X196" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="197" spans="21:24" x14ac:dyDescent="0.45">
@@ -6788,13 +7070,13 @@
         <v>112</v>
       </c>
       <c r="V197" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="W197" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="X197" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="198" spans="21:24" x14ac:dyDescent="0.45">
@@ -6802,13 +7084,13 @@
         <v>112</v>
       </c>
       <c r="V198" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="W198" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="X198" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="199" spans="21:24" x14ac:dyDescent="0.45">
@@ -6816,13 +7098,13 @@
         <v>112</v>
       </c>
       <c r="V199" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="W199" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="X199" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="200" spans="21:24" x14ac:dyDescent="0.45">
@@ -6830,13 +7112,13 @@
         <v>112</v>
       </c>
       <c r="V200" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="W200" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="X200" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="201" spans="21:24" x14ac:dyDescent="0.45">
@@ -6844,13 +7126,13 @@
         <v>112</v>
       </c>
       <c r="V201" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="W201" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="X201" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="202" spans="21:24" x14ac:dyDescent="0.45">
@@ -6858,13 +7140,13 @@
         <v>112</v>
       </c>
       <c r="V202" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="W202" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="X202" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="203" spans="21:24" x14ac:dyDescent="0.45">
@@ -6872,13 +7154,13 @@
         <v>112</v>
       </c>
       <c r="V203" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="W203" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="X203" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="204" spans="21:24" x14ac:dyDescent="0.45">
@@ -6886,13 +7168,13 @@
         <v>112</v>
       </c>
       <c r="V204" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="W204" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="X204" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="205" spans="21:24" x14ac:dyDescent="0.45">
@@ -6900,13 +7182,13 @@
         <v>112</v>
       </c>
       <c r="V205" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="W205" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="X205" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
     </row>
     <row r="206" spans="21:24" x14ac:dyDescent="0.45">
@@ -6914,13 +7196,13 @@
         <v>112</v>
       </c>
       <c r="V206" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="W206" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="X206" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="207" spans="21:24" x14ac:dyDescent="0.45">
@@ -6928,13 +7210,13 @@
         <v>112</v>
       </c>
       <c r="V207" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="W207" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="X207" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
     </row>
     <row r="208" spans="21:24" x14ac:dyDescent="0.45">
@@ -6942,13 +7224,13 @@
         <v>112</v>
       </c>
       <c r="V208" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="W208" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="X208" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="209" spans="21:24" x14ac:dyDescent="0.45">
@@ -6956,13 +7238,13 @@
         <v>112</v>
       </c>
       <c r="V209" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="W209" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="X209" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
     </row>
     <row r="210" spans="21:24" x14ac:dyDescent="0.45">
@@ -6970,13 +7252,13 @@
         <v>112</v>
       </c>
       <c r="V210" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="W210" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="X210" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="211" spans="21:24" x14ac:dyDescent="0.45">
@@ -6984,13 +7266,13 @@
         <v>112</v>
       </c>
       <c r="V211" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="W211" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="X211" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
     </row>
     <row r="212" spans="21:24" x14ac:dyDescent="0.45">
@@ -6998,13 +7280,13 @@
         <v>112</v>
       </c>
       <c r="V212" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="W212" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="X212" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="213" spans="21:24" x14ac:dyDescent="0.45">
@@ -7012,13 +7294,13 @@
         <v>112</v>
       </c>
       <c r="V213" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="W213" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="X213" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
     </row>
     <row r="214" spans="21:24" x14ac:dyDescent="0.45">
@@ -7026,13 +7308,13 @@
         <v>112</v>
       </c>
       <c r="V214" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="W214" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="X214" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="215" spans="21:24" x14ac:dyDescent="0.45">
@@ -7040,13 +7322,13 @@
         <v>112</v>
       </c>
       <c r="V215" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="W215" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="X215" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
     </row>
     <row r="216" spans="21:24" x14ac:dyDescent="0.45">
@@ -7054,13 +7336,13 @@
         <v>112</v>
       </c>
       <c r="V216" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="W216" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="X216" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="217" spans="21:24" x14ac:dyDescent="0.45">
@@ -7068,13 +7350,13 @@
         <v>112</v>
       </c>
       <c r="V217" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="W217" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="X217" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
     </row>
     <row r="218" spans="21:24" x14ac:dyDescent="0.45">
@@ -7082,13 +7364,13 @@
         <v>112</v>
       </c>
       <c r="V218" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="W218" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="X218" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="219" spans="21:24" x14ac:dyDescent="0.45">
@@ -7096,13 +7378,13 @@
         <v>112</v>
       </c>
       <c r="V219" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="W219" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="X219" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
     </row>
     <row r="220" spans="21:24" x14ac:dyDescent="0.45">
@@ -7110,13 +7392,13 @@
         <v>112</v>
       </c>
       <c r="V220" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="W220" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="X220" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="221" spans="21:24" x14ac:dyDescent="0.45">
@@ -7124,13 +7406,13 @@
         <v>112</v>
       </c>
       <c r="V221" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="W221" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="X221" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
     </row>
     <row r="222" spans="21:24" x14ac:dyDescent="0.45">
@@ -7138,13 +7420,13 @@
         <v>112</v>
       </c>
       <c r="V222" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="W222" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="X222" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="223" spans="21:24" x14ac:dyDescent="0.45">
@@ -7152,13 +7434,13 @@
         <v>112</v>
       </c>
       <c r="V223" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="W223" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="X223" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
     </row>
     <row r="224" spans="21:24" x14ac:dyDescent="0.45">
@@ -7166,13 +7448,13 @@
         <v>112</v>
       </c>
       <c r="V224" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="W224" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="X224" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="225" spans="21:24" x14ac:dyDescent="0.45">
@@ -7180,13 +7462,13 @@
         <v>112</v>
       </c>
       <c r="V225" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="W225" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="X225" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="226" spans="21:24" x14ac:dyDescent="0.45">
@@ -7194,13 +7476,13 @@
         <v>112</v>
       </c>
       <c r="V226" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="W226" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="X226" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="227" spans="21:24" x14ac:dyDescent="0.45">
@@ -7208,13 +7490,13 @@
         <v>112</v>
       </c>
       <c r="V227" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="W227" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="X227" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="228" spans="21:24" x14ac:dyDescent="0.45">
@@ -7222,13 +7504,13 @@
         <v>112</v>
       </c>
       <c r="V228" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="W228" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="X228" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="229" spans="21:24" x14ac:dyDescent="0.45">
@@ -7236,13 +7518,13 @@
         <v>112</v>
       </c>
       <c r="V229" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="W229" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="X229" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="230" spans="21:24" x14ac:dyDescent="0.45">
@@ -7250,13 +7532,13 @@
         <v>112</v>
       </c>
       <c r="V230" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="W230" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="X230" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="231" spans="21:24" x14ac:dyDescent="0.45">
@@ -7264,13 +7546,13 @@
         <v>112</v>
       </c>
       <c r="V231" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="W231" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="X231" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="232" spans="21:24" x14ac:dyDescent="0.45">
@@ -7278,13 +7560,13 @@
         <v>112</v>
       </c>
       <c r="V232" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="W232" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="X232" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="233" spans="21:24" x14ac:dyDescent="0.45">
@@ -7292,13 +7574,13 @@
         <v>112</v>
       </c>
       <c r="V233" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="W233" t="s">
+        <v>196</v>
+      </c>
+      <c r="X233" t="s">
         <v>194</v>
-      </c>
-      <c r="X233" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="234" spans="21:24" x14ac:dyDescent="0.45">
@@ -7306,13 +7588,13 @@
         <v>112</v>
       </c>
       <c r="V234" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="W234" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="X234" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="235" spans="21:24" x14ac:dyDescent="0.45">
@@ -7320,13 +7602,13 @@
         <v>112</v>
       </c>
       <c r="V235" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="W235" t="s">
+        <v>196</v>
+      </c>
+      <c r="X235" t="s">
         <v>194</v>
-      </c>
-      <c r="X235" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="236" spans="21:24" x14ac:dyDescent="0.45">
@@ -7334,13 +7616,13 @@
         <v>112</v>
       </c>
       <c r="V236" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="W236" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="X236" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="237" spans="21:24" x14ac:dyDescent="0.45">
@@ -7348,13 +7630,13 @@
         <v>112</v>
       </c>
       <c r="V237" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="W237" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="X237" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="238" spans="21:24" x14ac:dyDescent="0.45">
@@ -7362,13 +7644,13 @@
         <v>112</v>
       </c>
       <c r="V238" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="W238" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="X238" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="239" spans="21:24" x14ac:dyDescent="0.45">
@@ -7376,13 +7658,13 @@
         <v>112</v>
       </c>
       <c r="V239" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="W239" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="X239" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="240" spans="21:24" x14ac:dyDescent="0.45">
@@ -7390,13 +7672,13 @@
         <v>112</v>
       </c>
       <c r="V240" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="W240" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="X240" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="241" spans="21:24" x14ac:dyDescent="0.45">
@@ -7404,13 +7686,13 @@
         <v>112</v>
       </c>
       <c r="V241" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="W241" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="X241" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="242" spans="21:24" x14ac:dyDescent="0.45">
@@ -7418,13 +7700,13 @@
         <v>112</v>
       </c>
       <c r="V242" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="W242" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="X242" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="243" spans="21:24" x14ac:dyDescent="0.45">
@@ -7432,13 +7714,349 @@
         <v>112</v>
       </c>
       <c r="V243" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="W243" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="X243" t="s">
-        <v>187</v>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="244" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U244" t="s">
+        <v>112</v>
+      </c>
+      <c r="V244" t="s">
+        <v>415</v>
+      </c>
+      <c r="W244" t="s">
+        <v>199</v>
+      </c>
+      <c r="X244" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="245" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U245" t="s">
+        <v>112</v>
+      </c>
+      <c r="V245" t="s">
+        <v>415</v>
+      </c>
+      <c r="W245" t="s">
+        <v>199</v>
+      </c>
+      <c r="X245" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="246" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U246" t="s">
+        <v>112</v>
+      </c>
+      <c r="V246" t="s">
+        <v>416</v>
+      </c>
+      <c r="W246" t="s">
+        <v>199</v>
+      </c>
+      <c r="X246" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="247" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U247" t="s">
+        <v>112</v>
+      </c>
+      <c r="V247" t="s">
+        <v>416</v>
+      </c>
+      <c r="W247" t="s">
+        <v>199</v>
+      </c>
+      <c r="X247" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="248" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U248" t="s">
+        <v>112</v>
+      </c>
+      <c r="V248" t="s">
+        <v>417</v>
+      </c>
+      <c r="W248" t="s">
+        <v>200</v>
+      </c>
+      <c r="X248" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="249" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U249" t="s">
+        <v>112</v>
+      </c>
+      <c r="V249" t="s">
+        <v>417</v>
+      </c>
+      <c r="W249" t="s">
+        <v>200</v>
+      </c>
+      <c r="X249" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="250" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U250" t="s">
+        <v>112</v>
+      </c>
+      <c r="V250" t="s">
+        <v>418</v>
+      </c>
+      <c r="W250" t="s">
+        <v>200</v>
+      </c>
+      <c r="X250" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="251" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U251" t="s">
+        <v>112</v>
+      </c>
+      <c r="V251" t="s">
+        <v>418</v>
+      </c>
+      <c r="W251" t="s">
+        <v>200</v>
+      </c>
+      <c r="X251" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="252" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U252" t="s">
+        <v>112</v>
+      </c>
+      <c r="V252" t="s">
+        <v>419</v>
+      </c>
+      <c r="W252" t="s">
+        <v>201</v>
+      </c>
+      <c r="X252" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="253" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U253" t="s">
+        <v>112</v>
+      </c>
+      <c r="V253" t="s">
+        <v>419</v>
+      </c>
+      <c r="W253" t="s">
+        <v>201</v>
+      </c>
+      <c r="X253" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="254" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U254" t="s">
+        <v>112</v>
+      </c>
+      <c r="V254" t="s">
+        <v>420</v>
+      </c>
+      <c r="W254" t="s">
+        <v>201</v>
+      </c>
+      <c r="X254" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="255" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U255" t="s">
+        <v>112</v>
+      </c>
+      <c r="V255" t="s">
+        <v>420</v>
+      </c>
+      <c r="W255" t="s">
+        <v>201</v>
+      </c>
+      <c r="X255" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="256" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U256" t="s">
+        <v>112</v>
+      </c>
+      <c r="V256" t="s">
+        <v>421</v>
+      </c>
+      <c r="W256" t="s">
+        <v>202</v>
+      </c>
+      <c r="X256" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="257" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U257" t="s">
+        <v>112</v>
+      </c>
+      <c r="V257" t="s">
+        <v>421</v>
+      </c>
+      <c r="W257" t="s">
+        <v>202</v>
+      </c>
+      <c r="X257" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="258" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U258" t="s">
+        <v>112</v>
+      </c>
+      <c r="V258" t="s">
+        <v>422</v>
+      </c>
+      <c r="W258" t="s">
+        <v>202</v>
+      </c>
+      <c r="X258" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="259" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U259" t="s">
+        <v>112</v>
+      </c>
+      <c r="V259" t="s">
+        <v>422</v>
+      </c>
+      <c r="W259" t="s">
+        <v>202</v>
+      </c>
+      <c r="X259" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="260" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U260" t="s">
+        <v>112</v>
+      </c>
+      <c r="V260" t="s">
+        <v>423</v>
+      </c>
+      <c r="W260" t="s">
+        <v>203</v>
+      </c>
+      <c r="X260" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="261" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U261" t="s">
+        <v>112</v>
+      </c>
+      <c r="V261" t="s">
+        <v>423</v>
+      </c>
+      <c r="W261" t="s">
+        <v>203</v>
+      </c>
+      <c r="X261" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="262" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U262" t="s">
+        <v>112</v>
+      </c>
+      <c r="V262" t="s">
+        <v>424</v>
+      </c>
+      <c r="W262" t="s">
+        <v>203</v>
+      </c>
+      <c r="X262" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="263" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U263" t="s">
+        <v>112</v>
+      </c>
+      <c r="V263" t="s">
+        <v>424</v>
+      </c>
+      <c r="W263" t="s">
+        <v>203</v>
+      </c>
+      <c r="X263" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="264" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U264" t="s">
+        <v>112</v>
+      </c>
+      <c r="V264" t="s">
+        <v>425</v>
+      </c>
+      <c r="W264" t="s">
+        <v>204</v>
+      </c>
+      <c r="X264" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="265" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U265" t="s">
+        <v>112</v>
+      </c>
+      <c r="V265" t="s">
+        <v>425</v>
+      </c>
+      <c r="W265" t="s">
+        <v>204</v>
+      </c>
+      <c r="X265" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="266" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U266" t="s">
+        <v>112</v>
+      </c>
+      <c r="V266" t="s">
+        <v>426</v>
+      </c>
+      <c r="W266" t="s">
+        <v>204</v>
+      </c>
+      <c r="X266" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="267" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U267" t="s">
+        <v>112</v>
+      </c>
+      <c r="V267" t="s">
+        <v>426</v>
+      </c>
+      <c r="W267" t="s">
+        <v>204</v>
+      </c>
+      <c r="X267" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -7447,7 +8065,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F34AC98-A65F-4CC2-A60A-CB5D8FD01E9A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE130DC6-AB9E-4DC3-A860-F28DBB937D15}">
   <dimension ref="B9:L19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16034,8 +16652,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA5EA71F-D47B-4C06-B107-4F7EBA7BE363}">
-  <dimension ref="B2:Q33"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28D1885C-B5EE-4ADB-B547-6801C57BFA43}">
+  <dimension ref="B2:Q35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.45">
@@ -16057,7 +16675,7 @@
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>400</v>
+        <v>428</v>
       </c>
       <c r="E3" t="s">
         <v>26</v>
@@ -16066,7 +16684,7 @@
         <v>3</v>
       </c>
       <c r="I3" t="s">
-        <v>412</v>
+        <v>440</v>
       </c>
       <c r="N3" t="s">
         <v>29</v>
@@ -16075,27 +16693,27 @@
         <v>3</v>
       </c>
       <c r="P3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="Q3" t="s">
-        <v>423</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>410</v>
+        <v>438</v>
       </c>
       <c r="C4" t="s">
-        <v>411</v>
+        <v>439</v>
       </c>
       <c r="D4" t="s">
-        <v>401</v>
+        <v>429</v>
       </c>
       <c r="E4">
         <v>296000</v>
       </c>
       <c r="H4" t="s">
-        <v>413</v>
+        <v>441</v>
       </c>
       <c r="I4">
         <v>8.353368024319071E-3</v>
@@ -16104,10 +16722,10 @@
         <v>31</v>
       </c>
       <c r="O4" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="P4" t="s">
-        <v>424</v>
+        <v>453</v>
       </c>
       <c r="Q4">
         <v>0.95</v>
@@ -16115,7 +16733,7 @@
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.45">
       <c r="H5" t="s">
-        <v>414</v>
+        <v>442</v>
       </c>
       <c r="I5">
         <v>5.2830965408505251E-3</v>
@@ -16124,10 +16742,10 @@
         <v>31</v>
       </c>
       <c r="O5" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="P5" t="s">
-        <v>424</v>
+        <v>453</v>
       </c>
       <c r="Q5">
         <v>0.95</v>
@@ -16135,19 +16753,19 @@
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.45">
       <c r="H6" t="s">
-        <v>415</v>
+        <v>443</v>
       </c>
       <c r="I6">
-        <v>1.8079197649824548E-3</v>
+        <v>5.8577183209952656E-3</v>
       </c>
       <c r="N6" t="s">
         <v>31</v>
       </c>
       <c r="O6" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="P6" t="s">
-        <v>425</v>
+        <v>454</v>
       </c>
       <c r="Q6">
         <v>0.95</v>
@@ -16155,19 +16773,19 @@
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.45">
       <c r="H7" t="s">
-        <v>416</v>
+        <v>444</v>
       </c>
       <c r="I7">
-        <v>5.8577183209952656E-3</v>
+        <v>8.654925134073236E-3</v>
       </c>
       <c r="N7" t="s">
         <v>31</v>
       </c>
       <c r="O7" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="P7" t="s">
-        <v>425</v>
+        <v>454</v>
       </c>
       <c r="Q7">
         <v>0.95</v>
@@ -16175,19 +16793,19 @@
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.45">
       <c r="H8" t="s">
-        <v>417</v>
+        <v>445</v>
       </c>
       <c r="I8">
-        <v>8.654925134073236E-3</v>
+        <v>4.5521512959169706E-3</v>
       </c>
       <c r="N8" t="s">
         <v>31</v>
       </c>
       <c r="O8" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="P8" t="s">
-        <v>426</v>
+        <v>455</v>
       </c>
       <c r="Q8">
         <v>0.95</v>
@@ -16195,7 +16813,7 @@
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.45">
       <c r="H9" t="s">
-        <v>418</v>
+        <v>446</v>
       </c>
       <c r="I9">
         <v>5.8626230719278586E-3</v>
@@ -16204,10 +16822,10 @@
         <v>31</v>
       </c>
       <c r="O9" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="P9" t="s">
-        <v>426</v>
+        <v>455</v>
       </c>
       <c r="Q9">
         <v>0.95</v>
@@ -16215,19 +16833,19 @@
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.45">
       <c r="H10" t="s">
-        <v>419</v>
+        <v>447</v>
       </c>
       <c r="I10">
-        <v>4.1302097935766958E-3</v>
+        <v>3.9346713216003183E-3</v>
       </c>
       <c r="N10" t="s">
         <v>31</v>
       </c>
       <c r="O10" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="P10" t="s">
-        <v>427</v>
+        <v>456</v>
       </c>
       <c r="Q10">
         <v>0.95</v>
@@ -16235,7 +16853,7 @@
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.45">
       <c r="H11" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
       <c r="I11">
         <v>6.5670043628133726E-3</v>
@@ -16244,10 +16862,10 @@
         <v>31</v>
       </c>
       <c r="O11" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="P11" t="s">
-        <v>427</v>
+        <v>456</v>
       </c>
       <c r="Q11">
         <v>0.95</v>
@@ -16255,19 +16873,19 @@
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.45">
       <c r="H12" t="s">
-        <v>421</v>
+        <v>449</v>
       </c>
       <c r="I12">
-        <v>6.1152018933521336E-4</v>
+        <v>3.3496132492463033E-3</v>
       </c>
       <c r="N12" t="s">
         <v>31</v>
       </c>
       <c r="O12" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="P12" t="s">
-        <v>428</v>
+        <v>457</v>
       </c>
       <c r="Q12">
         <v>0.95</v>
@@ -16275,33 +16893,39 @@
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.45">
       <c r="H13" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="I13">
-        <v>3.3496132492463033E-3</v>
+        <v>7.9550716641029248E-3</v>
       </c>
       <c r="N13" t="s">
         <v>31</v>
       </c>
       <c r="O13" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="P13" t="s">
-        <v>428</v>
+        <v>457</v>
       </c>
       <c r="Q13">
         <v>0.95</v>
       </c>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="H14" t="s">
+        <v>451</v>
+      </c>
+      <c r="I14">
+        <v>3.8808596348135978E-4</v>
+      </c>
       <c r="N14" t="s">
         <v>31</v>
       </c>
       <c r="O14" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="P14" t="s">
-        <v>429</v>
+        <v>458</v>
       </c>
       <c r="Q14">
         <v>0.95</v>
@@ -16312,10 +16936,10 @@
         <v>31</v>
       </c>
       <c r="O15" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="P15" t="s">
-        <v>429</v>
+        <v>458</v>
       </c>
       <c r="Q15">
         <v>0.95</v>
@@ -16326,10 +16950,10 @@
         <v>31</v>
       </c>
       <c r="O16" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="P16" t="s">
-        <v>430</v>
+        <v>459</v>
       </c>
       <c r="Q16">
         <v>0.95</v>
@@ -16340,10 +16964,10 @@
         <v>31</v>
       </c>
       <c r="O17" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="P17" t="s">
-        <v>430</v>
+        <v>459</v>
       </c>
       <c r="Q17">
         <v>0.95</v>
@@ -16354,10 +16978,10 @@
         <v>31</v>
       </c>
       <c r="O18" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="P18" t="s">
-        <v>431</v>
+        <v>460</v>
       </c>
       <c r="Q18">
         <v>0.95</v>
@@ -16368,10 +16992,10 @@
         <v>31</v>
       </c>
       <c r="O19" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="P19" t="s">
-        <v>431</v>
+        <v>460</v>
       </c>
       <c r="Q19">
         <v>0.95</v>
@@ -16382,10 +17006,10 @@
         <v>31</v>
       </c>
       <c r="O20" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="P20" t="s">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="Q20">
         <v>0.95</v>
@@ -16396,10 +17020,10 @@
         <v>31</v>
       </c>
       <c r="O21" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="P21" t="s">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="Q21">
         <v>0.95</v>
@@ -16410,10 +17034,10 @@
         <v>31</v>
       </c>
       <c r="O22" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="P22" t="s">
-        <v>433</v>
+        <v>462</v>
       </c>
       <c r="Q22">
         <v>0.95</v>
@@ -16424,10 +17048,10 @@
         <v>31</v>
       </c>
       <c r="O23" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="P23" t="s">
-        <v>433</v>
+        <v>462</v>
       </c>
       <c r="Q23">
         <v>0.95</v>
@@ -16438,13 +17062,13 @@
         <v>31</v>
       </c>
       <c r="O24" t="s">
-        <v>434</v>
+        <v>390</v>
       </c>
       <c r="P24" t="s">
-        <v>432</v>
+        <v>463</v>
       </c>
       <c r="Q24">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="25" spans="14:17" x14ac:dyDescent="0.45">
@@ -16452,13 +17076,13 @@
         <v>31</v>
       </c>
       <c r="O25" t="s">
-        <v>435</v>
+        <v>400</v>
       </c>
       <c r="P25" t="s">
-        <v>430</v>
+        <v>463</v>
       </c>
       <c r="Q25">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="26" spans="14:17" x14ac:dyDescent="0.45">
@@ -16466,10 +17090,10 @@
         <v>31</v>
       </c>
       <c r="O26" t="s">
-        <v>436</v>
+        <v>464</v>
       </c>
       <c r="P26" t="s">
-        <v>427</v>
+        <v>463</v>
       </c>
       <c r="Q26">
         <v>0.85</v>
@@ -16480,10 +17104,10 @@
         <v>31</v>
       </c>
       <c r="O27" t="s">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="P27" t="s">
-        <v>432</v>
+        <v>459</v>
       </c>
       <c r="Q27">
         <v>0.85</v>
@@ -16494,10 +17118,10 @@
         <v>31</v>
       </c>
       <c r="O28" t="s">
-        <v>438</v>
+        <v>466</v>
       </c>
       <c r="P28" t="s">
-        <v>430</v>
+        <v>459</v>
       </c>
       <c r="Q28">
         <v>0.85</v>
@@ -16508,10 +17132,10 @@
         <v>31</v>
       </c>
       <c r="O29" t="s">
-        <v>439</v>
+        <v>467</v>
       </c>
       <c r="P29" t="s">
-        <v>432</v>
+        <v>455</v>
       </c>
       <c r="Q29">
         <v>0.85</v>
@@ -16522,10 +17146,10 @@
         <v>31</v>
       </c>
       <c r="O30" t="s">
-        <v>440</v>
+        <v>468</v>
       </c>
       <c r="P30" t="s">
-        <v>430</v>
+        <v>459</v>
       </c>
       <c r="Q30">
         <v>0.85</v>
@@ -16536,10 +17160,10 @@
         <v>31</v>
       </c>
       <c r="O31" t="s">
-        <v>441</v>
+        <v>469</v>
       </c>
       <c r="P31" t="s">
-        <v>424</v>
+        <v>459</v>
       </c>
       <c r="Q31">
         <v>0.85</v>
@@ -16550,10 +17174,10 @@
         <v>31</v>
       </c>
       <c r="O32" t="s">
-        <v>442</v>
+        <v>470</v>
       </c>
       <c r="P32" t="s">
-        <v>430</v>
+        <v>463</v>
       </c>
       <c r="Q32">
         <v>0.85</v>
@@ -16564,12 +17188,40 @@
         <v>31</v>
       </c>
       <c r="O33" t="s">
-        <v>443</v>
+        <v>471</v>
       </c>
       <c r="P33" t="s">
-        <v>428</v>
+        <v>453</v>
       </c>
       <c r="Q33">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="34" spans="14:17" x14ac:dyDescent="0.45">
+      <c r="N34" t="s">
+        <v>31</v>
+      </c>
+      <c r="O34" t="s">
+        <v>472</v>
+      </c>
+      <c r="P34" t="s">
+        <v>463</v>
+      </c>
+      <c r="Q34">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="35" spans="14:17" x14ac:dyDescent="0.45">
+      <c r="N35" t="s">
+        <v>31</v>
+      </c>
+      <c r="O35" t="s">
+        <v>473</v>
+      </c>
+      <c r="P35" t="s">
+        <v>456</v>
+      </c>
+      <c r="Q35">
         <v>0.85</v>
       </c>
     </row>
@@ -16579,13 +17231,13 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7F8C1F-0AC8-473E-B37F-A1B29BE3A159}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7586A6EE-0B47-4CCA-A2DB-55171F916EB9}">
   <dimension ref="A1:I28"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="C1" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
@@ -16593,12 +17245,12 @@
         <v>35</v>
       </c>
       <c r="G3" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>405</v>
+        <v>433</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
@@ -16607,10 +17259,10 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>446</v>
+        <v>476</v>
       </c>
       <c r="E4" t="s">
-        <v>447</v>
+        <v>477</v>
       </c>
       <c r="G4" t="s">
         <v>69</v>
@@ -16619,18 +17271,18 @@
         <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>446</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B5" t="s">
-        <v>449</v>
+        <v>479</v>
       </c>
       <c r="C5" t="s">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -16639,10 +17291,10 @@
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>449</v>
+        <v>479</v>
       </c>
       <c r="H5" t="s">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -16650,13 +17302,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B6" t="s">
-        <v>451</v>
+        <v>481</v>
       </c>
       <c r="C6" t="s">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -16665,10 +17317,10 @@
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>451</v>
+        <v>481</v>
       </c>
       <c r="H6" t="s">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -16676,13 +17328,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B7" t="s">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="C7" t="s">
-        <v>454</v>
+        <v>484</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -16691,10 +17343,10 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="H7" t="s">
-        <v>454</v>
+        <v>484</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -16702,13 +17354,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B8" t="s">
-        <v>455</v>
+        <v>485</v>
       </c>
       <c r="C8" t="s">
-        <v>456</v>
+        <v>486</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -16717,10 +17369,10 @@
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>455</v>
+        <v>485</v>
       </c>
       <c r="H8" t="s">
-        <v>456</v>
+        <v>486</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -16728,13 +17380,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B9" t="s">
-        <v>457</v>
+        <v>487</v>
       </c>
       <c r="C9" t="s">
-        <v>458</v>
+        <v>488</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -16743,10 +17395,10 @@
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>457</v>
+        <v>487</v>
       </c>
       <c r="H9" t="s">
-        <v>458</v>
+        <v>488</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -16754,13 +17406,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B10" t="s">
-        <v>459</v>
+        <v>489</v>
       </c>
       <c r="C10" t="s">
-        <v>460</v>
+        <v>490</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -16769,10 +17421,10 @@
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>459</v>
+        <v>489</v>
       </c>
       <c r="H10" t="s">
-        <v>460</v>
+        <v>490</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -16780,13 +17432,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B11" t="s">
-        <v>461</v>
+        <v>491</v>
       </c>
       <c r="C11" t="s">
-        <v>462</v>
+        <v>492</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -16795,10 +17447,10 @@
         <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>461</v>
+        <v>491</v>
       </c>
       <c r="H11" t="s">
-        <v>462</v>
+        <v>492</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -16806,13 +17458,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B12" t="s">
-        <v>463</v>
+        <v>493</v>
       </c>
       <c r="C12" t="s">
-        <v>464</v>
+        <v>494</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -16821,10 +17473,10 @@
         <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>463</v>
+        <v>493</v>
       </c>
       <c r="H12" t="s">
-        <v>464</v>
+        <v>494</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -16832,13 +17484,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B13" t="s">
-        <v>465</v>
+        <v>495</v>
       </c>
       <c r="C13" t="s">
-        <v>466</v>
+        <v>496</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -16847,10 +17499,10 @@
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>465</v>
+        <v>495</v>
       </c>
       <c r="H13" t="s">
-        <v>466</v>
+        <v>496</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -16858,13 +17510,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B14" t="s">
-        <v>467</v>
+        <v>497</v>
       </c>
       <c r="C14" t="s">
-        <v>468</v>
+        <v>498</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -16873,10 +17525,10 @@
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>467</v>
+        <v>497</v>
       </c>
       <c r="H14" t="s">
-        <v>468</v>
+        <v>498</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -16884,13 +17536,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B15" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="C15" t="s">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -16899,10 +17551,10 @@
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="H15" t="s">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -16910,13 +17562,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B16" t="s">
-        <v>471</v>
+        <v>501</v>
       </c>
       <c r="C16" t="s">
-        <v>472</v>
+        <v>502</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -16925,10 +17577,10 @@
         <v>2</v>
       </c>
       <c r="G16" t="s">
-        <v>471</v>
+        <v>501</v>
       </c>
       <c r="H16" t="s">
-        <v>472</v>
+        <v>502</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -16936,13 +17588,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B17" t="s">
-        <v>473</v>
+        <v>503</v>
       </c>
       <c r="C17" t="s">
-        <v>474</v>
+        <v>504</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -16951,10 +17603,10 @@
         <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>473</v>
+        <v>503</v>
       </c>
       <c r="H17" t="s">
-        <v>474</v>
+        <v>504</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -16962,13 +17614,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B18" t="s">
-        <v>475</v>
+        <v>505</v>
       </c>
       <c r="C18" t="s">
-        <v>476</v>
+        <v>506</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -16977,10 +17629,10 @@
         <v>2</v>
       </c>
       <c r="G18" t="s">
-        <v>475</v>
+        <v>505</v>
       </c>
       <c r="H18" t="s">
-        <v>476</v>
+        <v>506</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -16988,13 +17640,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B19" t="s">
-        <v>477</v>
+        <v>507</v>
       </c>
       <c r="C19" t="s">
-        <v>478</v>
+        <v>508</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -17003,10 +17655,10 @@
         <v>2</v>
       </c>
       <c r="G19" t="s">
-        <v>477</v>
+        <v>507</v>
       </c>
       <c r="H19" t="s">
-        <v>478</v>
+        <v>508</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -17014,13 +17666,13 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B20" t="s">
-        <v>479</v>
+        <v>509</v>
       </c>
       <c r="C20" t="s">
-        <v>480</v>
+        <v>510</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -17029,10 +17681,10 @@
         <v>2</v>
       </c>
       <c r="G20" t="s">
-        <v>479</v>
+        <v>509</v>
       </c>
       <c r="H20" t="s">
-        <v>480</v>
+        <v>510</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -17040,13 +17692,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B21" t="s">
-        <v>481</v>
+        <v>511</v>
       </c>
       <c r="C21" t="s">
-        <v>482</v>
+        <v>512</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -17055,10 +17707,10 @@
         <v>2</v>
       </c>
       <c r="G21" t="s">
-        <v>481</v>
+        <v>511</v>
       </c>
       <c r="H21" t="s">
-        <v>482</v>
+        <v>512</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -17066,13 +17718,13 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B22" t="s">
-        <v>483</v>
+        <v>513</v>
       </c>
       <c r="C22" t="s">
-        <v>484</v>
+        <v>514</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -17081,10 +17733,10 @@
         <v>2</v>
       </c>
       <c r="G22" t="s">
-        <v>483</v>
+        <v>513</v>
       </c>
       <c r="H22" t="s">
-        <v>484</v>
+        <v>514</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -17092,13 +17744,13 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B23" t="s">
-        <v>485</v>
+        <v>515</v>
       </c>
       <c r="C23" t="s">
-        <v>486</v>
+        <v>516</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -17107,10 +17759,10 @@
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>485</v>
+        <v>515</v>
       </c>
       <c r="H23" t="s">
-        <v>486</v>
+        <v>516</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -17118,13 +17770,13 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B24" t="s">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="C24" t="s">
-        <v>488</v>
+        <v>518</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -17133,10 +17785,10 @@
         <v>2</v>
       </c>
       <c r="G24" t="s">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="H24" t="s">
-        <v>488</v>
+        <v>518</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -17144,13 +17796,13 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B25" t="s">
-        <v>489</v>
+        <v>519</v>
       </c>
       <c r="C25" t="s">
-        <v>490</v>
+        <v>520</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -17159,10 +17811,10 @@
         <v>2</v>
       </c>
       <c r="G25" t="s">
-        <v>489</v>
+        <v>519</v>
       </c>
       <c r="H25" t="s">
-        <v>490</v>
+        <v>520</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -17170,13 +17822,13 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B26" t="s">
-        <v>491</v>
+        <v>521</v>
       </c>
       <c r="C26" t="s">
-        <v>492</v>
+        <v>522</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -17185,10 +17837,10 @@
         <v>2</v>
       </c>
       <c r="G26" t="s">
-        <v>491</v>
+        <v>521</v>
       </c>
       <c r="H26" t="s">
-        <v>492</v>
+        <v>522</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -17196,13 +17848,13 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B27" t="s">
-        <v>493</v>
+        <v>523</v>
       </c>
       <c r="C27" t="s">
-        <v>494</v>
+        <v>524</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -17211,10 +17863,10 @@
         <v>2</v>
       </c>
       <c r="G27" t="s">
-        <v>493</v>
+        <v>523</v>
       </c>
       <c r="H27" t="s">
-        <v>494</v>
+        <v>524</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -17222,13 +17874,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B28" t="s">
-        <v>495</v>
+        <v>525</v>
       </c>
       <c r="C28" t="s">
-        <v>496</v>
+        <v>526</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -17237,10 +17889,10 @@
         <v>2</v>
       </c>
       <c r="G28" t="s">
-        <v>495</v>
+        <v>525</v>
       </c>
       <c r="H28" t="s">
-        <v>496</v>
+        <v>526</v>
       </c>
       <c r="I28">
         <v>-1</v>
